--- a/广告预算控制-SPU监控表-20261024.xlsx
+++ b/广告预算控制-SPU监控表-20261024.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="668">
   <si>
     <t xml:space="preserve">分类</t>
   </si>
@@ -21937,6 +21937,12 @@
     <t xml:space="preserve">品线（分类）</t>
   </si>
   <si>
+    <t xml:space="preserve">广告状态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状态依据</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -21957,6 +21963,3550 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17.3% ≥17%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">维稳</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13.0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19.0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利润空间足（净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），但近 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天销售环比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-16%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，暂不加投</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19.0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16.0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">收缩</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7.6% &lt;8%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17.9% ≥17%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；近 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天销售环比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-81%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13.0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15.6%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-20%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17.8% ≥17%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.2% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">37%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-51%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.2% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">35%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-36%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.6%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10.2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-7.8% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-58%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-10.7% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-100%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天销售环比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-54%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利润空间足（净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">层面无加投项</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">46%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12.2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15.0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利润空间足（净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12.6%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">层面无加投项</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7.0% &lt;8%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">29.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，建议预算 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7.2% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.6%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">48%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天销售环比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-33%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天销售环比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-63%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-8.9% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">61%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-49%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.7% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">87%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.1% &lt;8%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21.7% ≥17%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，建议预算 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+2%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">57%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7.5% &lt;8%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利润空间足（净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">层面无加投项</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-2.1% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-55%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利润空间足（净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">层面无加投项</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天销售环比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-23%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11.6%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-26%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.3% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-49%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12.2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.6%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-2.4% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-34%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.2% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-43%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-3.2% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，建议预算 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+18%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7.3% &lt;8%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.9% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-40%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-2.9% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-60%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，建议预算 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+25%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天销售环比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-92%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天销售环比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-20%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天销售环比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-37%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-33.7% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-100%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-96.8% &lt;8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">99%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；建议预算较当前 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-90%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.6%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，在合理区间</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利润空间足（净毛利率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22.2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">层面无加投项</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">广告费率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17.6% ≥17%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">广告花费 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt;$2,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，影响小</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">广告状态判定（按顺序）：收缩＝净毛利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt;8% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">或 止损</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">压缩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">清理 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">或 建议预算较当前≤−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；观察＝广告费率≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">或 异常 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占广告≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">或 近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天销售环比≤−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；加投＝净毛利率≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、广告费率≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天环比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt;−10% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">且建议预算高于当前；其余维稳；广告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt;$2,000 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的小分类维稳。</t>
     </r>
   </si>
   <si>
@@ -22336,7 +25886,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -22443,6 +25993,13 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -22465,7 +26022,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFE7E6E6"/>
+      <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -22479,7 +26036,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFE7E6E6"/>
       <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -52696,19 +56253,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52716,36 +56275,42 @@
         <v>573</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>574</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="I1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="J1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="K1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="14" t="s">
-        <v>574</v>
-      </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="14" t="s">
+        <v>576</v>
+      </c>
+      <c r="M1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="N1" s="13" t="s">
         <v>23</v>
       </c>
     </row>
@@ -52753,47 +56318,53 @@
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A2)</f>
         <v>3843776.11</v>
       </c>
-      <c r="C2" s="5" t="n">
-        <f aca="false">B2/规则参数!$B$8</f>
+      <c r="E2" s="5" t="n">
+        <f aca="false">D2/规则参数!$B$8</f>
         <v>0.117635200591765</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="F2" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A2)</f>
         <v>319672.05</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <f aca="false">D2/规则参数!$B$9</f>
+      <c r="G2" s="5" t="n">
+        <f aca="false">F2/规则参数!$B$9</f>
         <v>0.0710522601547453</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A2)</f>
         <v>664904.02</v>
       </c>
-      <c r="G2" s="5" t="n">
-        <f aca="false">F2/规则参数!$B$10</f>
+      <c r="I2" s="5" t="n">
+        <f aca="false">H2/规则参数!$B$10</f>
         <v>0.137327555383146</v>
       </c>
-      <c r="H2" s="6" t="n">
-        <f aca="false">IFERROR(F2/B2,0)</f>
+      <c r="J2" s="6" t="n">
+        <f aca="false">IFERROR(H2/D2,0)</f>
         <v>0.172981984634896</v>
       </c>
-      <c r="I2" s="6" t="n">
-        <f aca="false">IFERROR(D2/B2,0)</f>
+      <c r="K2" s="6" t="n">
+        <f aca="false">IFERROR(F2/D2,0)</f>
         <v>0.0831661472603304</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="L2" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A2)</f>
         <v>8</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="M2" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A2)</f>
         <v>46907.5961284916</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="N2" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A2)</f>
         <v>38639.006295</v>
       </c>
@@ -52802,47 +56373,53 @@
       <c r="A3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A3)</f>
         <v>3339273.49</v>
       </c>
-      <c r="C3" s="5" t="n">
-        <f aca="false">B3/规则参数!$B$8</f>
+      <c r="E3" s="5" t="n">
+        <f aca="false">D3/规则参数!$B$8</f>
         <v>0.102195366115357</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="F3" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A3)</f>
         <v>433332.62</v>
       </c>
-      <c r="E3" s="5" t="n">
-        <f aca="false">D3/规则参数!$B$9</f>
+      <c r="G3" s="5" t="n">
+        <f aca="false">F3/规则参数!$B$9</f>
         <v>0.096315151886996</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A3)</f>
         <v>536394.27</v>
       </c>
-      <c r="G3" s="5" t="n">
-        <f aca="false">F3/规则参数!$B$10</f>
+      <c r="I3" s="5" t="n">
+        <f aca="false">H3/规则参数!$B$10</f>
         <v>0.110785484227675</v>
       </c>
-      <c r="H3" s="6" t="n">
-        <f aca="false">IFERROR(F3/B3,0)</f>
+      <c r="J3" s="6" t="n">
+        <f aca="false">IFERROR(H3/D3,0)</f>
         <v>0.160632027177864</v>
       </c>
-      <c r="I3" s="6" t="n">
-        <f aca="false">IFERROR(D3/B3,0)</f>
+      <c r="K3" s="6" t="n">
+        <f aca="false">IFERROR(F3/D3,0)</f>
         <v>0.129768532376185</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="L3" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A3)</f>
         <v>7</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="M3" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A3)</f>
         <v>62233.5754521112</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A3)</f>
         <v>59989.633701</v>
       </c>
@@ -52851,47 +56428,53 @@
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A4)</f>
         <v>3420028.95</v>
       </c>
-      <c r="C4" s="5" t="n">
-        <f aca="false">B4/规则参数!$B$8</f>
+      <c r="E4" s="5" t="n">
+        <f aca="false">D4/规则参数!$B$8</f>
         <v>0.104666812022747</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A4)</f>
         <v>495175.4</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <f aca="false">D4/规则参数!$B$9</f>
+      <c r="G4" s="5" t="n">
+        <f aca="false">F4/规则参数!$B$9</f>
         <v>0.110060705473094</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A4)</f>
         <v>467865.13</v>
       </c>
-      <c r="G4" s="5" t="n">
-        <f aca="false">F4/规则参数!$B$10</f>
+      <c r="I4" s="5" t="n">
+        <f aca="false">H4/规则参数!$B$10</f>
         <v>0.096631653019511</v>
       </c>
-      <c r="H4" s="6" t="n">
-        <f aca="false">IFERROR(F4/B4,0)</f>
+      <c r="J4" s="6" t="n">
+        <f aca="false">IFERROR(H4/D4,0)</f>
         <v>0.136801511577848</v>
       </c>
-      <c r="I4" s="6" t="n">
-        <f aca="false">IFERROR(D4/B4,0)</f>
+      <c r="K4" s="6" t="n">
+        <f aca="false">IFERROR(F4/D4,0)</f>
         <v>0.144786903046537</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="L4" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A4)</f>
         <v>10</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="M4" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A4)</f>
         <v>47876.7704714734</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="N4" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A4)</f>
         <v>48329.874268</v>
       </c>
@@ -52900,47 +56483,53 @@
       <c r="A5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A5)</f>
         <v>3088508.13</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <f aca="false">B5/规则参数!$B$8</f>
+      <c r="E5" s="5" t="n">
+        <f aca="false">D5/规则参数!$B$8</f>
         <v>0.0945209249978526</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A5)</f>
         <v>586491.97</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <f aca="false">D5/规则参数!$B$9</f>
+      <c r="G5" s="5" t="n">
+        <f aca="false">F5/规则参数!$B$9</f>
         <v>0.130357283444421</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A5)</f>
         <v>452612.54</v>
       </c>
-      <c r="G5" s="5" t="n">
-        <f aca="false">F5/规则参数!$B$10</f>
+      <c r="I5" s="5" t="n">
+        <f aca="false">H5/规则参数!$B$10</f>
         <v>0.0934814225577348</v>
       </c>
-      <c r="H5" s="6" t="n">
-        <f aca="false">IFERROR(F5/B5,0)</f>
+      <c r="J5" s="6" t="n">
+        <f aca="false">IFERROR(H5/D5,0)</f>
         <v>0.146547304053883</v>
       </c>
-      <c r="I5" s="6" t="n">
-        <f aca="false">IFERROR(D5/B5,0)</f>
+      <c r="K5" s="6" t="n">
+        <f aca="false">IFERROR(F5/D5,0)</f>
         <v>0.18989490890542</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="L5" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A5)</f>
         <v>38</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="M5" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A5)</f>
         <v>79835.446001184</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="N5" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A5)</f>
         <v>73515.556952</v>
       </c>
@@ -52949,47 +56538,53 @@
       <c r="A6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A6)</f>
         <v>2397143.87</v>
       </c>
-      <c r="C6" s="5" t="n">
-        <f aca="false">B6/规则参数!$B$8</f>
+      <c r="E6" s="5" t="n">
+        <f aca="false">D6/规则参数!$B$8</f>
         <v>0.0733623634480548</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A6)</f>
         <v>609510.08</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <f aca="false">D6/规则参数!$B$9</f>
+      <c r="G6" s="5" t="n">
+        <f aca="false">F6/规则参数!$B$9</f>
         <v>0.135473429006695</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A6)</f>
         <v>258949.19</v>
       </c>
-      <c r="G6" s="5" t="n">
-        <f aca="false">F6/规则参数!$B$10</f>
+      <c r="I6" s="5" t="n">
+        <f aca="false">H6/规则参数!$B$10</f>
         <v>0.0534826954891112</v>
       </c>
-      <c r="H6" s="6" t="n">
-        <f aca="false">IFERROR(F6/B6,0)</f>
+      <c r="J6" s="6" t="n">
+        <f aca="false">IFERROR(H6/D6,0)</f>
         <v>0.108024050304498</v>
       </c>
-      <c r="I6" s="6" t="n">
-        <f aca="false">IFERROR(D6/B6,0)</f>
+      <c r="K6" s="6" t="n">
+        <f aca="false">IFERROR(F6/D6,0)</f>
         <v>0.254265122601924</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="L6" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A6)</f>
         <v>8</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="M6" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A6)</f>
         <v>21227.979480914</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A6)</f>
         <v>22260.964174</v>
       </c>
@@ -52998,47 +56593,53 @@
       <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A7)</f>
         <v>1614868.73</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <f aca="false">B7/规则参数!$B$8</f>
+      <c r="E7" s="5" t="n">
+        <f aca="false">D7/规则参数!$B$8</f>
         <v>0.0494215587866066</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A7)</f>
         <v>307537.75</v>
       </c>
-      <c r="E7" s="5" t="n">
-        <f aca="false">D7/规则参数!$B$9</f>
+      <c r="G7" s="5" t="n">
+        <f aca="false">F7/规则参数!$B$9</f>
         <v>0.0683552166052835</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A7)</f>
         <v>258145.76</v>
       </c>
-      <c r="G7" s="5" t="n">
-        <f aca="false">F7/规则参数!$B$10</f>
+      <c r="I7" s="5" t="n">
+        <f aca="false">H7/规则参数!$B$10</f>
         <v>0.0533167571363524</v>
       </c>
-      <c r="H7" s="6" t="n">
-        <f aca="false">IFERROR(F7/B7,0)</f>
+      <c r="J7" s="6" t="n">
+        <f aca="false">IFERROR(H7/D7,0)</f>
         <v>0.159855569189206</v>
       </c>
-      <c r="I7" s="6" t="n">
-        <f aca="false">IFERROR(D7/B7,0)</f>
+      <c r="K7" s="6" t="n">
+        <f aca="false">IFERROR(F7/D7,0)</f>
         <v>0.190441330794733</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="L7" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A7)</f>
         <v>3</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="M7" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A7)</f>
         <v>19085.925011312</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A7)</f>
         <v>19052.144862</v>
       </c>
@@ -53047,47 +56648,53 @@
       <c r="A8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A8)</f>
         <v>1710642.63</v>
       </c>
-      <c r="C8" s="5" t="n">
-        <f aca="false">B8/规则参数!$B$8</f>
+      <c r="E8" s="5" t="n">
+        <f aca="false">D8/规则参数!$B$8</f>
         <v>0.0523526301121828</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A8)</f>
         <v>201720.85</v>
       </c>
-      <c r="E8" s="5" t="n">
-        <f aca="false">D8/规则参数!$B$9</f>
+      <c r="G8" s="5" t="n">
+        <f aca="false">F8/规则参数!$B$9</f>
         <v>0.0448357068215265</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A8)</f>
         <v>253472.5</v>
       </c>
-      <c r="G8" s="5" t="n">
-        <f aca="false">F8/规则参数!$B$10</f>
+      <c r="I8" s="5" t="n">
+        <f aca="false">H8/规则参数!$B$10</f>
         <v>0.0523515541113055</v>
       </c>
-      <c r="H8" s="6" t="n">
-        <f aca="false">IFERROR(F8/B8,0)</f>
+      <c r="J8" s="6" t="n">
+        <f aca="false">IFERROR(H8/D8,0)</f>
         <v>0.148173847392076</v>
       </c>
-      <c r="I8" s="6" t="n">
-        <f aca="false">IFERROR(D8/B8,0)</f>
+      <c r="K8" s="6" t="n">
+        <f aca="false">IFERROR(F8/D8,0)</f>
         <v>0.117921093782165</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="L8" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A8)</f>
         <v>14</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="M8" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A8)</f>
         <v>22900.4077599158</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="N8" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A8)</f>
         <v>22327.653595</v>
       </c>
@@ -53096,47 +56703,53 @@
       <c r="A9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A9)</f>
         <v>900793.65</v>
       </c>
-      <c r="C9" s="5" t="n">
-        <f aca="false">B9/规则参数!$B$8</f>
+      <c r="E9" s="5" t="n">
+        <f aca="false">D9/规则参数!$B$8</f>
         <v>0.027567953667712</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A9)</f>
         <v>117557.33</v>
       </c>
-      <c r="E9" s="5" t="n">
-        <f aca="false">D9/规则参数!$B$9</f>
+      <c r="G9" s="5" t="n">
+        <f aca="false">F9/规则参数!$B$9</f>
         <v>0.0261290093840148</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A9)</f>
         <v>126941.7</v>
       </c>
-      <c r="G9" s="5" t="n">
-        <f aca="false">F9/规则参数!$B$10</f>
+      <c r="I9" s="5" t="n">
+        <f aca="false">H9/规则参数!$B$10</f>
         <v>0.0262182101669061</v>
       </c>
-      <c r="H9" s="6" t="n">
-        <f aca="false">IFERROR(F9/B9,0)</f>
+      <c r="J9" s="6" t="n">
+        <f aca="false">IFERROR(H9/D9,0)</f>
         <v>0.140922063560284</v>
       </c>
-      <c r="I9" s="6" t="n">
-        <f aca="false">IFERROR(D9/B9,0)</f>
+      <c r="K9" s="6" t="n">
+        <f aca="false">IFERROR(F9/D9,0)</f>
         <v>0.130504172625995</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="L9" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A9)</f>
         <v>3</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="M9" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A9)</f>
         <v>13715.5700807405</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="N9" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A9)</f>
         <v>12669.29481</v>
       </c>
@@ -53145,47 +56758,53 @@
       <c r="A10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A10)</f>
         <v>779130.84</v>
       </c>
-      <c r="C10" s="5" t="n">
-        <f aca="false">B10/规则参数!$B$8</f>
+      <c r="E10" s="5" t="n">
+        <f aca="false">D10/规则参数!$B$8</f>
         <v>0.0238445762780472</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="F10" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A10)</f>
         <v>59132.01</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <f aca="false">D10/规则参数!$B$9</f>
+      <c r="G10" s="5" t="n">
+        <f aca="false">F10/规则参数!$B$9</f>
         <v>0.0131430413074681</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A10)</f>
         <v>123318.19</v>
       </c>
-      <c r="G10" s="5" t="n">
-        <f aca="false">F10/规则参数!$B$10</f>
+      <c r="I10" s="5" t="n">
+        <f aca="false">H10/规则参数!$B$10</f>
         <v>0.0254698197898914</v>
       </c>
-      <c r="H10" s="6" t="n">
-        <f aca="false">IFERROR(F10/B10,0)</f>
+      <c r="J10" s="6" t="n">
+        <f aca="false">IFERROR(H10/D10,0)</f>
         <v>0.158276612436494</v>
       </c>
-      <c r="I10" s="6" t="n">
-        <f aca="false">IFERROR(D10/B10,0)</f>
+      <c r="K10" s="6" t="n">
+        <f aca="false">IFERROR(F10/D10,0)</f>
         <v>0.0758948394341572</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="L10" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A10)</f>
         <v>4</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="M10" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A10)</f>
         <v>11988.2845773378</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="N10" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A10)</f>
         <v>9928.090842</v>
       </c>
@@ -53194,47 +56813,53 @@
       <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A11)</f>
         <v>684738.95</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <f aca="false">B11/规则参数!$B$8</f>
+      <c r="E11" s="5" t="n">
+        <f aca="false">D11/规则参数!$B$8</f>
         <v>0.0209558000859329</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A11)</f>
         <v>82943.24</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <f aca="false">D11/规则参数!$B$9</f>
+      <c r="G11" s="5" t="n">
+        <f aca="false">F11/规则参数!$B$9</f>
         <v>0.0184354705597736</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A11)</f>
         <v>122781.12</v>
       </c>
-      <c r="G11" s="5" t="n">
-        <f aca="false">F11/规则参数!$B$10</f>
+      <c r="I11" s="5" t="n">
+        <f aca="false">H11/规则参数!$B$10</f>
         <v>0.0253588947421385</v>
       </c>
-      <c r="H11" s="6" t="n">
-        <f aca="false">IFERROR(F11/B11,0)</f>
+      <c r="J11" s="6" t="n">
+        <f aca="false">IFERROR(H11/D11,0)</f>
         <v>0.179310845395899</v>
       </c>
-      <c r="I11" s="6" t="n">
-        <f aca="false">IFERROR(D11/B11,0)</f>
+      <c r="K11" s="6" t="n">
+        <f aca="false">IFERROR(F11/D11,0)</f>
         <v>0.121131184373256</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="L11" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A11)</f>
         <v>7</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="M11" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A11)</f>
         <v>1374.84439177558</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="N11" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A11)</f>
         <v>1178.45798</v>
       </c>
@@ -53243,47 +56868,53 @@
       <c r="A12" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A12)</f>
         <v>766016.84</v>
       </c>
-      <c r="C12" s="5" t="n">
-        <f aca="false">B12/规则参数!$B$8</f>
+      <c r="E12" s="5" t="n">
+        <f aca="false">D12/规则参数!$B$8</f>
         <v>0.0234432344786258</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A12)</f>
         <v>140298.33</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <f aca="false">D12/规则参数!$B$9</f>
+      <c r="G12" s="5" t="n">
+        <f aca="false">F12/规则参数!$B$9</f>
         <v>0.0311835627870385</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A12)</f>
         <v>113146.81</v>
       </c>
-      <c r="G12" s="5" t="n">
-        <f aca="false">F12/规则参数!$B$10</f>
+      <c r="I12" s="5" t="n">
+        <f aca="false">H12/规则参数!$B$10</f>
         <v>0.0233690492903041</v>
       </c>
-      <c r="H12" s="6" t="n">
-        <f aca="false">IFERROR(F12/B12,0)</f>
+      <c r="J12" s="6" t="n">
+        <f aca="false">IFERROR(H12/D12,0)</f>
         <v>0.147707992946996</v>
       </c>
-      <c r="I12" s="6" t="n">
-        <f aca="false">IFERROR(D12/B12,0)</f>
+      <c r="K12" s="6" t="n">
+        <f aca="false">IFERROR(F12/D12,0)</f>
         <v>0.183153062274714</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="L12" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A12)</f>
         <v>6</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="M12" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A12)</f>
         <v>12152.7709157129</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="N12" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A12)</f>
         <v>11917.108461</v>
       </c>
@@ -53292,47 +56923,53 @@
       <c r="A13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="D13" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A13)</f>
         <v>721986.1</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <f aca="false">B13/规则参数!$B$8</f>
+      <c r="E13" s="5" t="n">
+        <f aca="false">D13/规则参数!$B$8</f>
         <v>0.0220957145440935</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A13)</f>
         <v>93554.34</v>
       </c>
-      <c r="E13" s="5" t="n">
-        <f aca="false">D13/规则参数!$B$9</f>
+      <c r="G13" s="5" t="n">
+        <f aca="false">F13/规则参数!$B$9</f>
         <v>0.0207939583841799</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A13)</f>
         <v>112367.96</v>
       </c>
-      <c r="G13" s="5" t="n">
-        <f aca="false">F13/规则参数!$B$10</f>
+      <c r="I13" s="5" t="n">
+        <f aca="false">H13/规则参数!$B$10</f>
         <v>0.0232081876271273</v>
       </c>
-      <c r="H13" s="6" t="n">
-        <f aca="false">IFERROR(F13/B13,0)</f>
+      <c r="J13" s="6" t="n">
+        <f aca="false">IFERROR(H13/D13,0)</f>
         <v>0.155637289969987</v>
       </c>
-      <c r="I13" s="6" t="n">
-        <f aca="false">IFERROR(D13/B13,0)</f>
+      <c r="K13" s="6" t="n">
+        <f aca="false">IFERROR(F13/D13,0)</f>
         <v>0.129579142867155</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="L13" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A13)</f>
         <v>4</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="M13" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A13)</f>
         <v>3181.30661924693</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="N13" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A13)</f>
         <v>3181.603944</v>
       </c>
@@ -53341,47 +56978,53 @@
       <c r="A14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A14)</f>
         <v>664986.41</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <f aca="false">B14/规则参数!$B$8</f>
+      <c r="E14" s="5" t="n">
+        <f aca="false">D14/规则参数!$B$8</f>
         <v>0.0203512919307748</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A14)</f>
         <v>106801.42</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <f aca="false">D14/规则参数!$B$9</f>
+      <c r="G14" s="5" t="n">
+        <f aca="false">F14/规则参数!$B$9</f>
         <v>0.0237383352055215</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A14)</f>
         <v>83813.82</v>
       </c>
-      <c r="G14" s="5" t="n">
-        <f aca="false">F14/规则参数!$B$10</f>
+      <c r="I14" s="5" t="n">
+        <f aca="false">H14/规则参数!$B$10</f>
         <v>0.0173106894554842</v>
       </c>
-      <c r="H14" s="6" t="n">
-        <f aca="false">IFERROR(F14/B14,0)</f>
+      <c r="J14" s="6" t="n">
+        <f aca="false">IFERROR(H14/D14,0)</f>
         <v>0.12603839528089</v>
       </c>
-      <c r="I14" s="6" t="n">
-        <f aca="false">IFERROR(D14/B14,0)</f>
+      <c r="K14" s="6" t="n">
+        <f aca="false">IFERROR(F14/D14,0)</f>
         <v>0.160606921275278</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="L14" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A14)</f>
         <v>8</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="M14" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A14)</f>
         <v>5315.11406545414</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="N14" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A14)</f>
         <v>4236.492958</v>
       </c>
@@ -53390,47 +57033,53 @@
       <c r="A15" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="D15" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A15)</f>
         <v>383465.48</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <f aca="false">B15/规则参数!$B$8</f>
+      <c r="E15" s="5" t="n">
+        <f aca="false">D15/规则参数!$B$8</f>
         <v>0.0117356051364338</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A15)</f>
         <v>38476.57</v>
       </c>
-      <c r="E15" s="5" t="n">
-        <f aca="false">D15/规则参数!$B$9</f>
+      <c r="G15" s="5" t="n">
+        <f aca="false">F15/规则参数!$B$9</f>
         <v>0.00855203719406269</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A15)</f>
         <v>68101.34</v>
       </c>
-      <c r="G15" s="5" t="n">
-        <f aca="false">F15/规则参数!$B$10</f>
+      <c r="I15" s="5" t="n">
+        <f aca="false">H15/规则参数!$B$10</f>
         <v>0.0140654745033975</v>
       </c>
-      <c r="H15" s="6" t="n">
-        <f aca="false">IFERROR(F15/B15,0)</f>
+      <c r="J15" s="6" t="n">
+        <f aca="false">IFERROR(H15/D15,0)</f>
         <v>0.177594447354166</v>
       </c>
-      <c r="I15" s="6" t="n">
-        <f aca="false">IFERROR(D15/B15,0)</f>
+      <c r="K15" s="6" t="n">
+        <f aca="false">IFERROR(F15/D15,0)</f>
         <v>0.100339070938015</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="L15" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A15)</f>
         <v>3</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="M15" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A15)</f>
         <v>11232.8128938534</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="N15" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A15)</f>
         <v>9570.11568</v>
       </c>
@@ -53439,47 +57088,53 @@
       <c r="A16" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="D16" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A16)</f>
         <v>414857.34</v>
       </c>
-      <c r="C16" s="5" t="n">
-        <f aca="false">B16/规则参数!$B$8</f>
+      <c r="E16" s="5" t="n">
+        <f aca="false">D16/规则参数!$B$8</f>
         <v>0.0126963238782048</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="F16" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A16)</f>
         <v>63989.84</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <f aca="false">D16/规则参数!$B$9</f>
+      <c r="G16" s="5" t="n">
+        <f aca="false">F16/规则参数!$B$9</f>
         <v>0.0142227722409279</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A16)</f>
         <v>66768.04</v>
       </c>
-      <c r="G16" s="5" t="n">
-        <f aca="false">F16/规则参数!$B$10</f>
+      <c r="I16" s="5" t="n">
+        <f aca="false">H16/规则参数!$B$10</f>
         <v>0.0137900981722507</v>
       </c>
-      <c r="H16" s="6" t="n">
-        <f aca="false">IFERROR(F16/B16,0)</f>
+      <c r="J16" s="6" t="n">
+        <f aca="false">IFERROR(H16/D16,0)</f>
         <v>0.160942168698281</v>
       </c>
-      <c r="I16" s="6" t="n">
-        <f aca="false">IFERROR(D16/B16,0)</f>
+      <c r="K16" s="6" t="n">
+        <f aca="false">IFERROR(F16/D16,0)</f>
         <v>0.154245408795226</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="L16" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A16)</f>
         <v>4</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="M16" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A16)</f>
         <v>8010.43773783855</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="N16" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A16)</f>
         <v>7494.096648</v>
       </c>
@@ -53488,47 +57143,53 @@
       <c r="A17" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D17" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A17)</f>
         <v>481042.44</v>
       </c>
-      <c r="C17" s="5" t="n">
-        <f aca="false">B17/规则参数!$B$8</f>
+      <c r="E17" s="5" t="n">
+        <f aca="false">D17/规则参数!$B$8</f>
         <v>0.0147218574399621</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="F17" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A17)</f>
         <v>5871.27</v>
       </c>
-      <c r="E17" s="5" t="n">
-        <f aca="false">D17/规则参数!$B$9</f>
+      <c r="G17" s="5" t="n">
+        <f aca="false">F17/规则参数!$B$9</f>
         <v>0.00130498429086544</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A17)</f>
         <v>62094.62</v>
       </c>
-      <c r="G17" s="5" t="n">
-        <f aca="false">F17/规则参数!$B$10</f>
+      <c r="I17" s="5" t="n">
+        <f aca="false">H17/规则参数!$B$10</f>
         <v>0.0128248621012179</v>
       </c>
-      <c r="H17" s="6" t="n">
-        <f aca="false">IFERROR(F17/B17,0)</f>
+      <c r="J17" s="6" t="n">
+        <f aca="false">IFERROR(H17/D17,0)</f>
         <v>0.129083454673978</v>
       </c>
-      <c r="I17" s="6" t="n">
-        <f aca="false">IFERROR(D17/B17,0)</f>
+      <c r="K17" s="6" t="n">
+        <f aca="false">IFERROR(F17/D17,0)</f>
         <v>0.0122053056275035</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="L17" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A17)</f>
         <v>3</v>
       </c>
-      <c r="K17" s="4" t="n">
+      <c r="M17" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A17)</f>
         <v>1726.11175787045</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="N17" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A17)</f>
         <v>840.270704</v>
       </c>
@@ -53537,47 +57198,53 @@
       <c r="A18" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="D18" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A18)</f>
         <v>343918.41</v>
       </c>
-      <c r="C18" s="5" t="n">
-        <f aca="false">B18/规则参数!$B$8</f>
+      <c r="E18" s="5" t="n">
+        <f aca="false">D18/规则参数!$B$8</f>
         <v>0.0105253037611368</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="F18" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A18)</f>
         <v>17810.89</v>
       </c>
-      <c r="E18" s="5" t="n">
-        <f aca="false">D18/规则参数!$B$9</f>
+      <c r="G18" s="5" t="n">
+        <f aca="false">F18/规则参数!$B$9</f>
         <v>0.00395875707578298</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A18)</f>
         <v>60829.28</v>
       </c>
-      <c r="G18" s="5" t="n">
-        <f aca="false">F18/规则参数!$B$10</f>
+      <c r="I18" s="5" t="n">
+        <f aca="false">H18/规则参数!$B$10</f>
         <v>0.0125635220525767</v>
       </c>
-      <c r="H18" s="6" t="n">
-        <f aca="false">IFERROR(F18/B18,0)</f>
+      <c r="J18" s="6" t="n">
+        <f aca="false">IFERROR(H18/D18,0)</f>
         <v>0.176871252690427</v>
       </c>
-      <c r="I18" s="6" t="n">
-        <f aca="false">IFERROR(D18/B18,0)</f>
+      <c r="K18" s="6" t="n">
+        <f aca="false">IFERROR(F18/D18,0)</f>
         <v>0.0517881261430582</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="L18" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A18)</f>
         <v>5</v>
       </c>
-      <c r="K18" s="4" t="n">
+      <c r="M18" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A18)</f>
         <v>4791.13744499584</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="N18" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A18)</f>
         <v>4180.596005</v>
       </c>
@@ -53586,47 +57253,53 @@
       <c r="A19" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D19" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A19)</f>
         <v>225787.94</v>
       </c>
-      <c r="C19" s="5" t="n">
-        <f aca="false">B19/规则参数!$B$8</f>
+      <c r="E19" s="5" t="n">
+        <f aca="false">D19/规则参数!$B$8</f>
         <v>0.00691003035894863</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="F19" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A19)</f>
         <v>33293.86</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <f aca="false">D19/规则参数!$B$9</f>
+      <c r="G19" s="5" t="n">
+        <f aca="false">F19/规则参数!$B$9</f>
         <v>0.00740009644970734</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A19)</f>
         <v>60227.77</v>
       </c>
-      <c r="G19" s="5" t="n">
-        <f aca="false">F19/规则参数!$B$10</f>
+      <c r="I19" s="5" t="n">
+        <f aca="false">H19/规则参数!$B$10</f>
         <v>0.0124392877340077</v>
       </c>
-      <c r="H19" s="6" t="n">
-        <f aca="false">IFERROR(F19/B19,0)</f>
+      <c r="J19" s="6" t="n">
+        <f aca="false">IFERROR(H19/D19,0)</f>
         <v>0.266744849171307</v>
       </c>
-      <c r="I19" s="6" t="n">
-        <f aca="false">IFERROR(D19/B19,0)</f>
+      <c r="K19" s="6" t="n">
+        <f aca="false">IFERROR(F19/D19,0)</f>
         <v>0.147456325612431</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="L19" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A19)</f>
         <v>3</v>
       </c>
-      <c r="K19" s="4" t="n">
+      <c r="M19" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A19)</f>
         <v>5528.19203684928</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="N19" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A19)</f>
         <v>3554.814423</v>
       </c>
@@ -53635,47 +57308,53 @@
       <c r="A20" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D20" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A20)</f>
         <v>576464.5</v>
       </c>
-      <c r="C20" s="5" t="n">
-        <f aca="false">B20/规则参数!$B$8</f>
+      <c r="E20" s="5" t="n">
+        <f aca="false">D20/规则参数!$B$8</f>
         <v>0.0176421610288669</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="F20" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A20)</f>
         <v>84147.96</v>
       </c>
-      <c r="E20" s="5" t="n">
-        <f aca="false">D20/规则参数!$B$9</f>
+      <c r="G20" s="5" t="n">
+        <f aca="false">F20/规则参数!$B$9</f>
         <v>0.01870323897698</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A20)</f>
         <v>58835.22</v>
       </c>
-      <c r="G20" s="5" t="n">
-        <f aca="false">F20/规则参数!$B$10</f>
+      <c r="I20" s="5" t="n">
+        <f aca="false">H20/规则参数!$B$10</f>
         <v>0.012151674061212</v>
       </c>
-      <c r="H20" s="6" t="n">
-        <f aca="false">IFERROR(F20/B20,0)</f>
+      <c r="J20" s="6" t="n">
+        <f aca="false">IFERROR(H20/D20,0)</f>
         <v>0.102062173819897</v>
       </c>
-      <c r="I20" s="6" t="n">
-        <f aca="false">IFERROR(D20/B20,0)</f>
+      <c r="K20" s="6" t="n">
+        <f aca="false">IFERROR(F20/D20,0)</f>
         <v>0.145972492668673</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="L20" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A20)</f>
         <v>5</v>
       </c>
-      <c r="K20" s="4" t="n">
+      <c r="M20" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A20)</f>
         <v>6163.09791689484</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="N20" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A20)</f>
         <v>5963.986994</v>
       </c>
@@ -53684,47 +57363,53 @@
       <c r="A21" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="D21" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A21)</f>
         <v>344802.08</v>
       </c>
-      <c r="C21" s="5" t="n">
-        <f aca="false">B21/规则参数!$B$8</f>
+      <c r="E21" s="5" t="n">
+        <f aca="false">D21/规则参数!$B$8</f>
         <v>0.0105523476613881</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="F21" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A21)</f>
         <v>46666.06</v>
       </c>
-      <c r="E21" s="5" t="n">
-        <f aca="false">D21/规则参数!$B$9</f>
+      <c r="G21" s="5" t="n">
+        <f aca="false">F21/规则参数!$B$9</f>
         <v>0.010372283205607</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A21)</f>
         <v>56212.4</v>
       </c>
-      <c r="G21" s="5" t="n">
-        <f aca="false">F21/规则参数!$B$10</f>
+      <c r="I21" s="5" t="n">
+        <f aca="false">H21/规则参数!$B$10</f>
         <v>0.0116099636068069</v>
       </c>
-      <c r="H21" s="6" t="n">
-        <f aca="false">IFERROR(F21/B21,0)</f>
+      <c r="J21" s="6" t="n">
+        <f aca="false">IFERROR(H21/D21,0)</f>
         <v>0.163028018856499</v>
       </c>
-      <c r="I21" s="6" t="n">
-        <f aca="false">IFERROR(D21/B21,0)</f>
+      <c r="K21" s="6" t="n">
+        <f aca="false">IFERROR(F21/D21,0)</f>
         <v>0.135341584946355</v>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="L21" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A21)</f>
         <v>12</v>
       </c>
-      <c r="K21" s="4" t="n">
+      <c r="M21" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A21)</f>
         <v>6521.20703437198</v>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="N21" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A21)</f>
         <v>5407.878479</v>
       </c>
@@ -53733,47 +57418,53 @@
       <c r="A22" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D22" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A22)</f>
         <v>241125.61</v>
       </c>
-      <c r="C22" s="5" t="n">
-        <f aca="false">B22/规则参数!$B$8</f>
+      <c r="E22" s="5" t="n">
+        <f aca="false">D22/规则参数!$B$8</f>
         <v>0.00737942551502089</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="F22" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A22)</f>
         <v>-18861.89</v>
       </c>
-      <c r="E22" s="5" t="n">
-        <f aca="false">D22/规则参数!$B$9</f>
+      <c r="G22" s="5" t="n">
+        <f aca="false">F22/规则参数!$B$9</f>
         <v>-0.00419235874794242</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A22)</f>
         <v>47078.54</v>
       </c>
-      <c r="G22" s="5" t="n">
-        <f aca="false">F22/规则参数!$B$10</f>
+      <c r="I22" s="5" t="n">
+        <f aca="false">H22/规则参数!$B$10</f>
         <v>0.00972347980270547</v>
       </c>
-      <c r="H22" s="6" t="n">
-        <f aca="false">IFERROR(F22/B22,0)</f>
+      <c r="J22" s="6" t="n">
+        <f aca="false">IFERROR(H22/D22,0)</f>
         <v>0.195244876726284</v>
       </c>
-      <c r="I22" s="6" t="n">
-        <f aca="false">IFERROR(D22/B22,0)</f>
+      <c r="K22" s="6" t="n">
+        <f aca="false">IFERROR(F22/D22,0)</f>
         <v>-0.0782243329524392</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="L22" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A22)</f>
         <v>3</v>
       </c>
-      <c r="K22" s="4" t="n">
+      <c r="M22" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A22)</f>
         <v>3808.44946310265</v>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="N22" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A22)</f>
         <v>1584.836977</v>
       </c>
@@ -53782,47 +57473,53 @@
       <c r="A23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D23" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A23)</f>
         <v>344145.18</v>
       </c>
-      <c r="C23" s="5" t="n">
-        <f aca="false">B23/规则参数!$B$8</f>
+      <c r="E23" s="5" t="n">
+        <f aca="false">D23/规则参数!$B$8</f>
         <v>0.0105322438465307</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="F23" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A23)</f>
         <v>-36953.05</v>
       </c>
-      <c r="E23" s="5" t="n">
-        <f aca="false">D23/规则参数!$B$9</f>
+      <c r="G23" s="5" t="n">
+        <f aca="false">F23/规则参数!$B$9</f>
         <v>-0.00821341034385493</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A23)</f>
         <v>44617.11</v>
       </c>
-      <c r="G23" s="5" t="n">
-        <f aca="false">F23/规则参数!$B$10</f>
+      <c r="I23" s="5" t="n">
+        <f aca="false">H23/规则参数!$B$10</f>
         <v>0.00921510242118996</v>
       </c>
-      <c r="H23" s="6" t="n">
-        <f aca="false">IFERROR(F23/B23,0)</f>
+      <c r="J23" s="6" t="n">
+        <f aca="false">IFERROR(H23/D23,0)</f>
         <v>0.129646185949779</v>
       </c>
-      <c r="I23" s="6" t="n">
-        <f aca="false">IFERROR(D23/B23,0)</f>
+      <c r="K23" s="6" t="n">
+        <f aca="false">IFERROR(F23/D23,0)</f>
         <v>-0.107376340415403</v>
       </c>
-      <c r="J23" s="3" t="n">
+      <c r="L23" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A23)</f>
         <v>1</v>
       </c>
-      <c r="K23" s="4" t="n">
+      <c r="M23" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A23)</f>
         <v>2015.58202726216</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="N23" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A23)</f>
         <v>0</v>
       </c>
@@ -53831,47 +57528,53 @@
       <c r="A24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="D24" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A24)</f>
         <v>267894.4</v>
       </c>
-      <c r="C24" s="5" t="n">
-        <f aca="false">B24/规则参数!$B$8</f>
+      <c r="E24" s="5" t="n">
+        <f aca="false">D24/规则参数!$B$8</f>
         <v>0.00819865948992815</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="F24" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A24)</f>
         <v>50441.16</v>
       </c>
-      <c r="E24" s="5" t="n">
-        <f aca="false">D24/规则参数!$B$9</f>
+      <c r="G24" s="5" t="n">
+        <f aca="false">F24/规则参数!$B$9</f>
         <v>0.0112113599635224</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A24)</f>
         <v>44150.66</v>
       </c>
-      <c r="G24" s="5" t="n">
-        <f aca="false">F24/规则参数!$B$10</f>
+      <c r="I24" s="5" t="n">
+        <f aca="false">H24/规则参数!$B$10</f>
         <v>0.009118763045458</v>
       </c>
-      <c r="H24" s="6" t="n">
-        <f aca="false">IFERROR(F24/B24,0)</f>
+      <c r="J24" s="6" t="n">
+        <f aca="false">IFERROR(H24/D24,0)</f>
         <v>0.16480620722195</v>
       </c>
-      <c r="I24" s="6" t="n">
-        <f aca="false">IFERROR(D24/B24,0)</f>
+      <c r="K24" s="6" t="n">
+        <f aca="false">IFERROR(F24/D24,0)</f>
         <v>0.188287474467551</v>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="L24" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A24)</f>
         <v>1</v>
       </c>
-      <c r="K24" s="4" t="n">
+      <c r="M24" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A24)</f>
         <v>1355.61180944208</v>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="N24" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A24)</f>
         <v>1355.560752</v>
       </c>
@@ -53880,47 +57583,53 @@
       <c r="A25" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D25" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A25)</f>
         <v>324725.53</v>
       </c>
-      <c r="C25" s="5" t="n">
-        <f aca="false">B25/规则参数!$B$8</f>
+      <c r="E25" s="5" t="n">
+        <f aca="false">D25/规则参数!$B$8</f>
         <v>0.0099379234808807</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="F25" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A25)</f>
         <v>53500.56</v>
       </c>
-      <c r="E25" s="5" t="n">
-        <f aca="false">D25/规则参数!$B$9</f>
+      <c r="G25" s="5" t="n">
+        <f aca="false">F25/规则参数!$B$9</f>
         <v>0.0118913608729464</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A25)</f>
         <v>41439.44</v>
       </c>
-      <c r="G25" s="5" t="n">
-        <f aca="false">F25/规则参数!$B$10</f>
+      <c r="I25" s="5" t="n">
+        <f aca="false">H25/规则参数!$B$10</f>
         <v>0.00855879468385012</v>
       </c>
-      <c r="H25" s="6" t="n">
-        <f aca="false">IFERROR(F25/B25,0)</f>
+      <c r="J25" s="6" t="n">
+        <f aca="false">IFERROR(H25/D25,0)</f>
         <v>0.127613741980805</v>
       </c>
-      <c r="I25" s="6" t="n">
-        <f aca="false">IFERROR(D25/B25,0)</f>
+      <c r="K25" s="6" t="n">
+        <f aca="false">IFERROR(F25/D25,0)</f>
         <v>0.164756248145934</v>
       </c>
-      <c r="J25" s="3" t="n">
+      <c r="L25" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A25)</f>
         <v>2</v>
       </c>
-      <c r="K25" s="4" t="n">
+      <c r="M25" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A25)</f>
         <v>7645.06682709765</v>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="N25" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A25)</f>
         <v>6933.063091</v>
       </c>
@@ -53929,47 +57638,53 @@
       <c r="A26" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="D26" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A26)</f>
         <v>180695</v>
       </c>
-      <c r="C26" s="5" t="n">
-        <f aca="false">B26/规则参数!$B$8</f>
+      <c r="E26" s="5" t="n">
+        <f aca="false">D26/规则参数!$B$8</f>
         <v>0.00553000277920168</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="F26" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A26)</f>
         <v>18981.46</v>
       </c>
-      <c r="E26" s="5" t="n">
-        <f aca="false">D26/规则参数!$B$9</f>
+      <c r="G26" s="5" t="n">
+        <f aca="false">F26/规则参数!$B$9</f>
         <v>0.00421893510563996</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A26)</f>
         <v>41303.73</v>
       </c>
-      <c r="G26" s="5" t="n">
-        <f aca="false">F26/规则参数!$B$10</f>
+      <c r="I26" s="5" t="n">
+        <f aca="false">H26/规则参数!$B$10</f>
         <v>0.00853076549169536</v>
       </c>
-      <c r="H26" s="6" t="n">
-        <f aca="false">IFERROR(F26/B26,0)</f>
+      <c r="J26" s="6" t="n">
+        <f aca="false">IFERROR(H26/D26,0)</f>
         <v>0.228582583912117</v>
       </c>
-      <c r="I26" s="6" t="n">
-        <f aca="false">IFERROR(D26/B26,0)</f>
+      <c r="K26" s="6" t="n">
+        <f aca="false">IFERROR(F26/D26,0)</f>
         <v>0.105046957580453</v>
       </c>
-      <c r="J26" s="3" t="n">
+      <c r="L26" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A26)</f>
         <v>2</v>
       </c>
-      <c r="K26" s="4" t="n">
+      <c r="M26" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A26)</f>
         <v>6878.60412231609</v>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="N26" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A26)</f>
         <v>5973.2604</v>
       </c>
@@ -53978,47 +57693,53 @@
       <c r="A27" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D27" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A27)</f>
         <v>271360.02</v>
       </c>
-      <c r="C27" s="5" t="n">
-        <f aca="false">B27/规则参数!$B$8</f>
+      <c r="E27" s="5" t="n">
+        <f aca="false">D27/规则参数!$B$8</f>
         <v>0.00830472157372491</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="F27" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A27)</f>
         <v>40097.51</v>
       </c>
-      <c r="E27" s="5" t="n">
-        <f aca="false">D27/规则参数!$B$9</f>
+      <c r="G27" s="5" t="n">
+        <f aca="false">F27/规则参数!$B$9</f>
         <v>0.00891231720783065</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A27)</f>
         <v>35422.04</v>
       </c>
-      <c r="G27" s="5" t="n">
-        <f aca="false">F27/规则参数!$B$10</f>
+      <c r="I27" s="5" t="n">
+        <f aca="false">H27/规则参数!$B$10</f>
         <v>0.00731597646211257</v>
       </c>
-      <c r="H27" s="6" t="n">
-        <f aca="false">IFERROR(F27/B27,0)</f>
+      <c r="J27" s="6" t="n">
+        <f aca="false">IFERROR(H27/D27,0)</f>
         <v>0.130535220332015</v>
       </c>
-      <c r="I27" s="6" t="n">
-        <f aca="false">IFERROR(D27/B27,0)</f>
+      <c r="K27" s="6" t="n">
+        <f aca="false">IFERROR(F27/D27,0)</f>
         <v>0.147764987635246</v>
       </c>
-      <c r="J27" s="3" t="n">
+      <c r="L27" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A27)</f>
         <v>1</v>
       </c>
-      <c r="K27" s="4" t="n">
+      <c r="M27" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A27)</f>
         <v>4067.73592528185</v>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="N27" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A27)</f>
         <v>4066.63839</v>
       </c>
@@ -54027,47 +57748,53 @@
       <c r="A28" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="D28" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A28)</f>
         <v>281390.22</v>
       </c>
-      <c r="C28" s="5" t="n">
-        <f aca="false">B28/规则参数!$B$8</f>
+      <c r="E28" s="5" t="n">
+        <f aca="false">D28/规则参数!$B$8</f>
         <v>0.00861168653609769</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="F28" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A28)</f>
         <v>33940.2</v>
       </c>
-      <c r="E28" s="5" t="n">
-        <f aca="false">D28/规则参数!$B$9</f>
+      <c r="G28" s="5" t="n">
+        <f aca="false">F28/规则参数!$B$9</f>
         <v>0.00754375592143287</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A28)</f>
         <v>34379.96</v>
       </c>
-      <c r="G28" s="5" t="n">
-        <f aca="false">F28/规则参数!$B$10</f>
+      <c r="I28" s="5" t="n">
+        <f aca="false">H28/规则参数!$B$10</f>
         <v>0.00710074795602884</v>
       </c>
-      <c r="H28" s="6" t="n">
-        <f aca="false">IFERROR(F28/B28,0)</f>
+      <c r="J28" s="6" t="n">
+        <f aca="false">IFERROR(H28/D28,0)</f>
         <v>0.122178944243336</v>
       </c>
-      <c r="I28" s="6" t="n">
-        <f aca="false">IFERROR(D28/B28,0)</f>
+      <c r="K28" s="6" t="n">
+        <f aca="false">IFERROR(F28/D28,0)</f>
         <v>0.120616132287753</v>
       </c>
-      <c r="J28" s="3" t="n">
+      <c r="L28" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A28)</f>
         <v>2</v>
       </c>
-      <c r="K28" s="4" t="n">
+      <c r="M28" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A28)</f>
         <v>3105.61241282476</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="N28" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A28)</f>
         <v>3106.420626</v>
       </c>
@@ -54076,47 +57803,53 @@
       <c r="A29" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D29" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A29)</f>
         <v>222954.6</v>
       </c>
-      <c r="C29" s="5" t="n">
-        <f aca="false">B29/规则参数!$B$8</f>
+      <c r="E29" s="5" t="n">
+        <f aca="false">D29/规则参数!$B$8</f>
         <v>0.00682331861775809</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="F29" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A29)</f>
         <v>28246.7</v>
       </c>
-      <c r="E29" s="5" t="n">
-        <f aca="false">D29/规则参数!$B$9</f>
+      <c r="G29" s="5" t="n">
+        <f aca="false">F29/规则参数!$B$9</f>
         <v>0.00627828387534363</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A29)</f>
         <v>33463.36</v>
       </c>
-      <c r="G29" s="5" t="n">
-        <f aca="false">F29/规则参数!$B$10</f>
+      <c r="I29" s="5" t="n">
+        <f aca="false">H29/规则参数!$B$10</f>
         <v>0.00691143576437719</v>
       </c>
-      <c r="H29" s="6" t="n">
-        <f aca="false">IFERROR(F29/B29,0)</f>
+      <c r="J29" s="6" t="n">
+        <f aca="false">IFERROR(H29/D29,0)</f>
         <v>0.150090466848408</v>
       </c>
-      <c r="I29" s="6" t="n">
-        <f aca="false">IFERROR(D29/B29,0)</f>
+      <c r="K29" s="6" t="n">
+        <f aca="false">IFERROR(F29/D29,0)</f>
         <v>0.126692609167965</v>
       </c>
-      <c r="J29" s="3" t="n">
+      <c r="L29" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A29)</f>
         <v>2</v>
       </c>
-      <c r="K29" s="4" t="n">
+      <c r="M29" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A29)</f>
         <v>3838.40894896505</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="N29" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A29)</f>
         <v>3328.95646</v>
       </c>
@@ -54125,47 +57858,53 @@
       <c r="A30" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D30" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A30)</f>
         <v>247807.96</v>
       </c>
-      <c r="C30" s="5" t="n">
-        <f aca="false">B30/规则参数!$B$8</f>
+      <c r="E30" s="5" t="n">
+        <f aca="false">D30/规则参数!$B$8</f>
         <v>0.00758393263514928</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="F30" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A30)</f>
         <v>39050.01</v>
       </c>
-      <c r="E30" s="5" t="n">
-        <f aca="false">D30/规则参数!$B$9</f>
+      <c r="G30" s="5" t="n">
+        <f aca="false">F30/规则参数!$B$9</f>
         <v>0.00867949346702474</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A30)</f>
         <v>31268.17</v>
       </c>
-      <c r="G30" s="5" t="n">
-        <f aca="false">F30/规则参数!$B$10</f>
+      <c r="I30" s="5" t="n">
+        <f aca="false">H30/规则参数!$B$10</f>
         <v>0.00645804690337808</v>
       </c>
-      <c r="H30" s="6" t="n">
-        <f aca="false">IFERROR(F30/B30,0)</f>
+      <c r="J30" s="6" t="n">
+        <f aca="false">IFERROR(H30/D30,0)</f>
         <v>0.126179037993776</v>
       </c>
-      <c r="I30" s="6" t="n">
-        <f aca="false">IFERROR(D30/B30,0)</f>
+      <c r="K30" s="6" t="n">
+        <f aca="false">IFERROR(F30/D30,0)</f>
         <v>0.157581741926288</v>
       </c>
-      <c r="J30" s="3" t="n">
+      <c r="L30" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A30)</f>
         <v>5</v>
       </c>
-      <c r="K30" s="4" t="n">
+      <c r="M30" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A30)</f>
         <v>4649.06258244006</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="N30" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A30)</f>
         <v>4398.890539</v>
       </c>
@@ -54174,47 +57913,53 @@
       <c r="A31" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D31" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A31)</f>
         <v>257103.73</v>
       </c>
-      <c r="C31" s="5" t="n">
-        <f aca="false">B31/规则参数!$B$8</f>
+      <c r="E31" s="5" t="n">
+        <f aca="false">D31/规则参数!$B$8</f>
         <v>0.00786842104896715</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="F31" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A31)</f>
         <v>18078.48</v>
       </c>
-      <c r="E31" s="5" t="n">
-        <f aca="false">D31/规则参数!$B$9</f>
+      <c r="G31" s="5" t="n">
+        <f aca="false">F31/规则参数!$B$9</f>
         <v>0.00401823326175172</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A31)</f>
         <v>29731.62</v>
       </c>
-      <c r="G31" s="5" t="n">
-        <f aca="false">F31/规则参数!$B$10</f>
+      <c r="I31" s="5" t="n">
+        <f aca="false">H31/规则参数!$B$10</f>
         <v>0.00614069184328388</v>
       </c>
-      <c r="H31" s="6" t="n">
-        <f aca="false">IFERROR(F31/B31,0)</f>
+      <c r="J31" s="6" t="n">
+        <f aca="false">IFERROR(H31/D31,0)</f>
         <v>0.115640562663171</v>
       </c>
-      <c r="I31" s="6" t="n">
-        <f aca="false">IFERROR(D31/B31,0)</f>
+      <c r="K31" s="6" t="n">
+        <f aca="false">IFERROR(F31/D31,0)</f>
         <v>0.0703158993453732</v>
       </c>
-      <c r="J31" s="3" t="n">
+      <c r="L31" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A31)</f>
         <v>9</v>
       </c>
-      <c r="K31" s="4" t="n">
+      <c r="M31" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A31)</f>
         <v>4477.71526974537</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="N31" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A31)</f>
         <v>4136.402737</v>
       </c>
@@ -54223,47 +57968,53 @@
       <c r="A32" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D32" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A32)</f>
         <v>300917.23</v>
       </c>
-      <c r="C32" s="5" t="n">
-        <f aca="false">B32/规则参数!$B$8</f>
+      <c r="E32" s="5" t="n">
+        <f aca="false">D32/规则参数!$B$8</f>
         <v>0.00920929255491115</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="F32" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A32)</f>
         <v>89554.13</v>
       </c>
-      <c r="E32" s="5" t="n">
-        <f aca="false">D32/规则参数!$B$9</f>
+      <c r="G32" s="5" t="n">
+        <f aca="false">F32/规则参数!$B$9</f>
         <v>0.0199048473042666</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A32)</f>
         <v>26885.37</v>
       </c>
-      <c r="G32" s="5" t="n">
-        <f aca="false">F32/规则参数!$B$10</f>
+      <c r="I32" s="5" t="n">
+        <f aca="false">H32/规则参数!$B$10</f>
         <v>0.00555283473496127</v>
       </c>
-      <c r="H32" s="6" t="n">
-        <f aca="false">IFERROR(F32/B32,0)</f>
+      <c r="J32" s="6" t="n">
+        <f aca="false">IFERROR(H32/D32,0)</f>
         <v>0.0893447344307935</v>
       </c>
-      <c r="I32" s="6" t="n">
-        <f aca="false">IFERROR(D32/B32,0)</f>
+      <c r="K32" s="6" t="n">
+        <f aca="false">IFERROR(F32/D32,0)</f>
         <v>0.297603862696729</v>
       </c>
-      <c r="J32" s="3" t="n">
+      <c r="L32" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A32)</f>
         <v>1</v>
       </c>
-      <c r="K32" s="4" t="n">
+      <c r="M32" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A32)</f>
         <v>2780.0150186548</v>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="N32" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A32)</f>
         <v>3612.52116</v>
       </c>
@@ -54272,47 +58023,53 @@
       <c r="A33" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="D33" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A33)</f>
         <v>132067.7</v>
       </c>
-      <c r="C33" s="5" t="n">
-        <f aca="false">B33/规则参数!$B$8</f>
+      <c r="E33" s="5" t="n">
+        <f aca="false">D33/规则参数!$B$8</f>
         <v>0.00404180939175281</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="F33" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A33)</f>
         <v>9539.49</v>
       </c>
-      <c r="E33" s="5" t="n">
-        <f aca="false">D33/规则参数!$B$9</f>
+      <c r="G33" s="5" t="n">
+        <f aca="false">F33/规则参数!$B$9</f>
         <v>0.00212030524790513</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A33)</f>
         <v>24793.01</v>
       </c>
-      <c r="G33" s="5" t="n">
-        <f aca="false">F33/规则参数!$B$10</f>
+      <c r="I33" s="5" t="n">
+        <f aca="false">H33/规则参数!$B$10</f>
         <v>0.00512068411601708</v>
       </c>
-      <c r="H33" s="6" t="n">
-        <f aca="false">IFERROR(F33/B33,0)</f>
+      <c r="J33" s="6" t="n">
+        <f aca="false">IFERROR(H33/D33,0)</f>
         <v>0.187729550828855</v>
       </c>
-      <c r="I33" s="6" t="n">
-        <f aca="false">IFERROR(D33/B33,0)</f>
+      <c r="K33" s="6" t="n">
+        <f aca="false">IFERROR(F33/D33,0)</f>
         <v>0.0722318174693737</v>
       </c>
-      <c r="J33" s="3" t="n">
+      <c r="L33" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A33)</f>
         <v>6</v>
       </c>
-      <c r="K33" s="4" t="n">
+      <c r="M33" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A33)</f>
         <v>4110.81206124979</v>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="N33" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A33)</f>
         <v>3539.193397</v>
       </c>
@@ -54321,47 +58078,53 @@
       <c r="A34" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="D34" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A34)</f>
         <v>193380.3</v>
       </c>
-      <c r="C34" s="5" t="n">
-        <f aca="false">B34/规则参数!$B$8</f>
+      <c r="E34" s="5" t="n">
+        <f aca="false">D34/规则参数!$B$8</f>
         <v>0.0059182246129824</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="F34" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A34)</f>
         <v>28277.75</v>
       </c>
-      <c r="E34" s="5" t="n">
-        <f aca="false">D34/规则参数!$B$9</f>
+      <c r="G34" s="5" t="n">
+        <f aca="false">F34/规则参数!$B$9</f>
         <v>0.00628518523777993</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A34)</f>
         <v>24506.63</v>
       </c>
-      <c r="G34" s="5" t="n">
-        <f aca="false">F34/规则参数!$B$10</f>
+      <c r="I34" s="5" t="n">
+        <f aca="false">H34/规则参数!$B$10</f>
         <v>0.00506153593202712</v>
       </c>
-      <c r="H34" s="6" t="n">
-        <f aca="false">IFERROR(F34/B34,0)</f>
+      <c r="J34" s="6" t="n">
+        <f aca="false">IFERROR(H34/D34,0)</f>
         <v>0.126727644956596</v>
       </c>
-      <c r="I34" s="6" t="n">
-        <f aca="false">IFERROR(D34/B34,0)</f>
+      <c r="K34" s="6" t="n">
+        <f aca="false">IFERROR(F34/D34,0)</f>
         <v>0.146228700648411</v>
       </c>
-      <c r="J34" s="3" t="n">
+      <c r="L34" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A34)</f>
         <v>3</v>
       </c>
-      <c r="K34" s="4" t="n">
+      <c r="M34" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A34)</f>
         <v>2096.02340972298</v>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="N34" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A34)</f>
         <v>1924.305016</v>
       </c>
@@ -54370,47 +58133,53 @@
       <c r="A35" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B35" s="4" t="n">
+      <c r="B35" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="D35" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A35)</f>
         <v>110084.47</v>
       </c>
-      <c r="C35" s="5" t="n">
-        <f aca="false">B35/规则参数!$B$8</f>
+      <c r="E35" s="5" t="n">
+        <f aca="false">D35/规则参数!$B$8</f>
         <v>0.00336903303935883</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="F35" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A35)</f>
         <v>9863.16</v>
       </c>
-      <c r="E35" s="5" t="n">
-        <f aca="false">D35/规则参数!$B$9</f>
+      <c r="G35" s="5" t="n">
+        <f aca="false">F35/规则参数!$B$9</f>
         <v>0.0021922461168184</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A35)</f>
         <v>20227.91</v>
       </c>
-      <c r="G35" s="5" t="n">
-        <f aca="false">F35/规则参数!$B$10</f>
+      <c r="I35" s="5" t="n">
+        <f aca="false">H35/规则参数!$B$10</f>
         <v>0.00417782017742997</v>
       </c>
-      <c r="H35" s="6" t="n">
-        <f aca="false">IFERROR(F35/B35,0)</f>
+      <c r="J35" s="6" t="n">
+        <f aca="false">IFERROR(H35/D35,0)</f>
         <v>0.183748988390461</v>
       </c>
-      <c r="I35" s="6" t="n">
-        <f aca="false">IFERROR(D35/B35,0)</f>
+      <c r="K35" s="6" t="n">
+        <f aca="false">IFERROR(F35/D35,0)</f>
         <v>0.0895962891041761</v>
       </c>
-      <c r="J35" s="3" t="n">
+      <c r="L35" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A35)</f>
         <v>3</v>
       </c>
-      <c r="K35" s="4" t="n">
+      <c r="M35" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A35)</f>
         <v>1897.75023065793</v>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="N35" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A35)</f>
         <v>1611.8701</v>
       </c>
@@ -54419,47 +58188,53 @@
       <c r="A36" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="D36" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A36)</f>
         <v>137287.78</v>
       </c>
-      <c r="C36" s="5" t="n">
-        <f aca="false">B36/规则参数!$B$8</f>
+      <c r="E36" s="5" t="n">
+        <f aca="false">D36/规则参数!$B$8</f>
         <v>0.00420156509560546</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="F36" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A36)</f>
         <v>17043.6</v>
       </c>
-      <c r="E36" s="5" t="n">
-        <f aca="false">D36/规则参数!$B$9</f>
+      <c r="G36" s="5" t="n">
+        <f aca="false">F36/规则参数!$B$9</f>
         <v>0.00378821451914053</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A36)</f>
         <v>18119.99</v>
       </c>
-      <c r="G36" s="5" t="n">
-        <f aca="false">F36/规则参数!$B$10</f>
+      <c r="I36" s="5" t="n">
+        <f aca="false">H36/规则参数!$B$10</f>
         <v>0.00374245583635824</v>
       </c>
-      <c r="H36" s="6" t="n">
-        <f aca="false">IFERROR(F36/B36,0)</f>
+      <c r="J36" s="6" t="n">
+        <f aca="false">IFERROR(H36/D36,0)</f>
         <v>0.1319854542043</v>
       </c>
-      <c r="I36" s="6" t="n">
-        <f aca="false">IFERROR(D36/B36,0)</f>
+      <c r="K36" s="6" t="n">
+        <f aca="false">IFERROR(F36/D36,0)</f>
         <v>0.124145062291779</v>
       </c>
-      <c r="J36" s="3" t="n">
+      <c r="L36" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A36)</f>
         <v>1</v>
       </c>
-      <c r="K36" s="4" t="n">
+      <c r="M36" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A36)</f>
         <v>1872.17275239719</v>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="N36" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A36)</f>
         <v>1872.37908</v>
       </c>
@@ -54468,47 +58243,53 @@
       <c r="A37" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="B37" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="D37" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A37)</f>
         <v>181053.77</v>
       </c>
-      <c r="C37" s="5" t="n">
-        <f aca="false">B37/规则参数!$B$8</f>
+      <c r="E37" s="5" t="n">
+        <f aca="false">D37/规则参数!$B$8</f>
         <v>0.0055409826020916</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="F37" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A37)</f>
         <v>22070.61</v>
       </c>
-      <c r="E37" s="5" t="n">
-        <f aca="false">D37/规则参数!$B$9</f>
+      <c r="G37" s="5" t="n">
+        <f aca="false">F37/规则参数!$B$9</f>
         <v>0.00490554843156892</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A37)</f>
         <v>18003.16</v>
       </c>
-      <c r="G37" s="5" t="n">
-        <f aca="false">F37/规则参数!$B$10</f>
+      <c r="I37" s="5" t="n">
+        <f aca="false">H37/规则参数!$B$10</f>
         <v>0.00371832607053819</v>
       </c>
-      <c r="H37" s="6" t="n">
-        <f aca="false">IFERROR(F37/B37,0)</f>
+      <c r="J37" s="6" t="n">
+        <f aca="false">IFERROR(H37/D37,0)</f>
         <v>0.0994354329103448</v>
       </c>
-      <c r="I37" s="6" t="n">
-        <f aca="false">IFERROR(D37/B37,0)</f>
+      <c r="K37" s="6" t="n">
+        <f aca="false">IFERROR(F37/D37,0)</f>
         <v>0.121900858512916</v>
       </c>
-      <c r="J37" s="3" t="n">
+      <c r="L37" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A37)</f>
         <v>2</v>
       </c>
-      <c r="K37" s="4" t="n">
+      <c r="M37" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A37)</f>
         <v>854.047069726422</v>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="N37" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A37)</f>
         <v>854.3817</v>
       </c>
@@ -54517,47 +58298,53 @@
       <c r="A38" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="B38" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="D38" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A38)</f>
         <v>109200.6</v>
       </c>
-      <c r="C38" s="5" t="n">
-        <f aca="false">B38/规则参数!$B$8</f>
+      <c r="E38" s="5" t="n">
+        <f aca="false">D38/规则参数!$B$8</f>
         <v>0.00334198301829321</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="F38" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A38)</f>
         <v>8875.52</v>
       </c>
-      <c r="E38" s="5" t="n">
-        <f aca="false">D38/规则参数!$B$9</f>
+      <c r="G38" s="5" t="n">
+        <f aca="false">F38/规则参数!$B$9</f>
         <v>0.00197272722481882</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A38)</f>
         <v>16960.62</v>
       </c>
-      <c r="G38" s="5" t="n">
-        <f aca="false">F38/规则参数!$B$10</f>
+      <c r="I38" s="5" t="n">
+        <f aca="false">H38/规则参数!$B$10</f>
         <v>0.00350300255724503</v>
       </c>
-      <c r="H38" s="6" t="n">
-        <f aca="false">IFERROR(F38/B38,0)</f>
+      <c r="J38" s="6" t="n">
+        <f aca="false">IFERROR(H38/D38,0)</f>
         <v>0.155316179581431</v>
       </c>
-      <c r="I38" s="6" t="n">
-        <f aca="false">IFERROR(D38/B38,0)</f>
+      <c r="K38" s="6" t="n">
+        <f aca="false">IFERROR(F38/D38,0)</f>
         <v>0.0812772090995837</v>
       </c>
-      <c r="J38" s="3" t="n">
+      <c r="L38" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A38)</f>
         <v>2</v>
       </c>
-      <c r="K38" s="4" t="n">
+      <c r="M38" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A38)</f>
         <v>1116.35778563842</v>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="N38" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A38)</f>
         <v>982.38448</v>
       </c>
@@ -54566,47 +58353,53 @@
       <c r="A39" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B39" s="4" t="n">
+      <c r="B39" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="D39" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A39)</f>
         <v>78066.35</v>
       </c>
-      <c r="C39" s="5" t="n">
-        <f aca="false">B39/规则参数!$B$8</f>
+      <c r="E39" s="5" t="n">
+        <f aca="false">D39/规则参数!$B$8</f>
         <v>0.00238914819149468</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="F39" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A39)</f>
         <v>-6850.72</v>
       </c>
-      <c r="E39" s="5" t="n">
-        <f aca="false">D39/规则参数!$B$9</f>
+      <c r="G39" s="5" t="n">
+        <f aca="false">F39/规则参数!$B$9</f>
         <v>-0.00152268282349776</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A39)</f>
         <v>16599.6</v>
       </c>
-      <c r="G39" s="5" t="n">
-        <f aca="false">F39/规则参数!$B$10</f>
+      <c r="I39" s="5" t="n">
+        <f aca="false">H39/规则参数!$B$10</f>
         <v>0.00342843842083866</v>
       </c>
-      <c r="H39" s="6" t="n">
-        <f aca="false">IFERROR(F39/B39,0)</f>
+      <c r="J39" s="6" t="n">
+        <f aca="false">IFERROR(H39/D39,0)</f>
         <v>0.21263450897858</v>
       </c>
-      <c r="I39" s="6" t="n">
-        <f aca="false">IFERROR(D39/B39,0)</f>
+      <c r="K39" s="6" t="n">
+        <f aca="false">IFERROR(F39/D39,0)</f>
         <v>-0.0877550955052977</v>
       </c>
-      <c r="J39" s="3" t="n">
+      <c r="L39" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A39)</f>
         <v>3</v>
       </c>
-      <c r="K39" s="4" t="n">
+      <c r="M39" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A39)</f>
         <v>2773.70237345721</v>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="N39" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A39)</f>
         <v>1414.77232</v>
       </c>
@@ -54615,47 +58408,53 @@
       <c r="A40" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="B40" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D40" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A40)</f>
         <v>151929.9</v>
       </c>
-      <c r="C40" s="5" t="n">
-        <f aca="false">B40/规则参数!$B$8</f>
+      <c r="E40" s="5" t="n">
+        <f aca="false">D40/规则参数!$B$8</f>
         <v>0.00464967358943985</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="F40" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A40)</f>
         <v>6148.52</v>
       </c>
-      <c r="E40" s="5" t="n">
-        <f aca="false">D40/规则参数!$B$9</f>
+      <c r="G40" s="5" t="n">
+        <f aca="false">F40/规则参数!$B$9</f>
         <v>0.00136660756736992</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A40)</f>
         <v>16357.91</v>
       </c>
-      <c r="G40" s="5" t="n">
-        <f aca="false">F40/规则参数!$B$10</f>
+      <c r="I40" s="5" t="n">
+        <f aca="false">H40/规则参数!$B$10</f>
         <v>0.00337852039378183</v>
       </c>
-      <c r="H40" s="6" t="n">
-        <f aca="false">IFERROR(F40/B40,0)</f>
+      <c r="J40" s="6" t="n">
+        <f aca="false">IFERROR(H40/D40,0)</f>
         <v>0.107667483490741</v>
       </c>
-      <c r="I40" s="6" t="n">
-        <f aca="false">IFERROR(D40/B40,0)</f>
+      <c r="K40" s="6" t="n">
+        <f aca="false">IFERROR(F40/D40,0)</f>
         <v>0.0404694533465763</v>
       </c>
-      <c r="J40" s="3" t="n">
+      <c r="L40" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A40)</f>
         <v>10</v>
       </c>
-      <c r="K40" s="4" t="n">
+      <c r="M40" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A40)</f>
         <v>1366.82544291825</v>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="N40" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A40)</f>
         <v>1292.443045</v>
       </c>
@@ -54664,47 +58463,53 @@
       <c r="A41" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B41" s="4" t="n">
+      <c r="B41" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="D41" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A41)</f>
         <v>126292.99</v>
       </c>
-      <c r="C41" s="5" t="n">
-        <f aca="false">B41/规则参数!$B$8</f>
+      <c r="E41" s="5" t="n">
+        <f aca="false">D41/规则参数!$B$8</f>
         <v>0.00386507975148006</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="F41" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A41)</f>
         <v>7737.53</v>
       </c>
-      <c r="E41" s="5" t="n">
-        <f aca="false">D41/规则参数!$B$9</f>
+      <c r="G41" s="5" t="n">
+        <f aca="false">F41/规则参数!$B$9</f>
         <v>0.00171979062453269</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A41)</f>
         <v>16256.21</v>
       </c>
-      <c r="G41" s="5" t="n">
-        <f aca="false">F41/规则参数!$B$10</f>
+      <c r="I41" s="5" t="n">
+        <f aca="false">H41/规则参数!$B$10</f>
         <v>0.00335751553900224</v>
       </c>
-      <c r="H41" s="6" t="n">
-        <f aca="false">IFERROR(F41/B41,0)</f>
+      <c r="J41" s="6" t="n">
+        <f aca="false">IFERROR(H41/D41,0)</f>
         <v>0.128718228937331</v>
       </c>
-      <c r="I41" s="6" t="n">
-        <f aca="false">IFERROR(D41/B41,0)</f>
+      <c r="K41" s="6" t="n">
+        <f aca="false">IFERROR(F41/D41,0)</f>
         <v>0.0612665041820611</v>
       </c>
-      <c r="J41" s="3" t="n">
+      <c r="L41" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A41)</f>
         <v>2</v>
       </c>
-      <c r="K41" s="4" t="n">
+      <c r="M41" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A41)</f>
         <v>3907.69105361651</v>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="N41" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A41)</f>
         <v>3179.470125</v>
       </c>
@@ -54713,47 +58518,53 @@
       <c r="A42" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="B42" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="D42" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A42)</f>
         <v>73817.39</v>
       </c>
-      <c r="C42" s="5" t="n">
-        <f aca="false">B42/规则参数!$B$8</f>
+      <c r="E42" s="5" t="n">
+        <f aca="false">D42/规则参数!$B$8</f>
         <v>0.00225911271398442</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="F42" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A42)</f>
         <v>7182.38</v>
       </c>
-      <c r="E42" s="5" t="n">
-        <f aca="false">D42/规则参数!$B$9</f>
+      <c r="G42" s="5" t="n">
+        <f aca="false">F42/规则参数!$B$9</f>
         <v>0.00159639959855808</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A42)</f>
         <v>16028.59</v>
       </c>
-      <c r="G42" s="5" t="n">
-        <f aca="false">F42/规则参数!$B$10</f>
+      <c r="I42" s="5" t="n">
+        <f aca="false">H42/规则参数!$B$10</f>
         <v>0.00331050349332938</v>
       </c>
-      <c r="H42" s="6" t="n">
-        <f aca="false">IFERROR(F42/B42,0)</f>
+      <c r="J42" s="6" t="n">
+        <f aca="false">IFERROR(H42/D42,0)</f>
         <v>0.217138400585553</v>
       </c>
-      <c r="I42" s="6" t="n">
-        <f aca="false">IFERROR(D42/B42,0)</f>
+      <c r="K42" s="6" t="n">
+        <f aca="false">IFERROR(F42/D42,0)</f>
         <v>0.0972992949222399</v>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="L42" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A42)</f>
         <v>2</v>
       </c>
-      <c r="K42" s="4" t="n">
+      <c r="M42" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A42)</f>
         <v>2856.26819790487</v>
       </c>
-      <c r="L42" s="4" t="n">
+      <c r="N42" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A42)</f>
         <v>2855.71314</v>
       </c>
@@ -54762,47 +58573,53 @@
       <c r="A43" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B43" s="4" t="n">
+      <c r="B43" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D43" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A43)</f>
         <v>136802.94</v>
       </c>
-      <c r="C43" s="5" t="n">
-        <f aca="false">B43/规则参数!$B$8</f>
+      <c r="E43" s="5" t="n">
+        <f aca="false">D43/规则参数!$B$8</f>
         <v>0.00418672701736606</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="F43" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A43)</f>
         <v>22860.61</v>
       </c>
-      <c r="E43" s="5" t="n">
-        <f aca="false">D43/规则参数!$B$9</f>
+      <c r="G43" s="5" t="n">
+        <f aca="false">F43/规则参数!$B$9</f>
         <v>0.00508113865136527</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A43)</f>
         <v>15626.58</v>
       </c>
-      <c r="G43" s="5" t="n">
-        <f aca="false">F43/规则参数!$B$10</f>
+      <c r="I43" s="5" t="n">
+        <f aca="false">H43/规则参数!$B$10</f>
         <v>0.00322747338841352</v>
       </c>
-      <c r="H43" s="6" t="n">
-        <f aca="false">IFERROR(F43/B43,0)</f>
+      <c r="J43" s="6" t="n">
+        <f aca="false">IFERROR(H43/D43,0)</f>
         <v>0.114226931087885</v>
       </c>
-      <c r="I43" s="6" t="n">
-        <f aca="false">IFERROR(D43/B43,0)</f>
+      <c r="K43" s="6" t="n">
+        <f aca="false">IFERROR(F43/D43,0)</f>
         <v>0.167106130906251</v>
       </c>
-      <c r="J43" s="3" t="n">
+      <c r="L43" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A43)</f>
         <v>3</v>
       </c>
-      <c r="K43" s="4" t="n">
+      <c r="M43" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A43)</f>
         <v>2745.59863209494</v>
       </c>
-      <c r="L43" s="4" t="n">
+      <c r="N43" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A43)</f>
         <v>2800.763719</v>
       </c>
@@ -54811,47 +58628,53 @@
       <c r="A44" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="B44" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="D44" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A44)</f>
         <v>85434.91</v>
       </c>
-      <c r="C44" s="5" t="n">
-        <f aca="false">B44/规则参数!$B$8</f>
+      <c r="E44" s="5" t="n">
+        <f aca="false">D44/规则参数!$B$8</f>
         <v>0.00261465613182902</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="F44" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A44)</f>
         <v>7966.39</v>
       </c>
-      <c r="E44" s="5" t="n">
-        <f aca="false">D44/规则参数!$B$9</f>
+      <c r="G44" s="5" t="n">
+        <f aca="false">F44/规则参数!$B$9</f>
         <v>0.00177065844440939</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A44)</f>
         <v>14239.57</v>
       </c>
-      <c r="G44" s="5" t="n">
-        <f aca="false">F44/规则参数!$B$10</f>
+      <c r="I44" s="5" t="n">
+        <f aca="false">H44/规则参数!$B$10</f>
         <v>0.0029410039328792</v>
       </c>
-      <c r="H44" s="6" t="n">
-        <f aca="false">IFERROR(F44/B44,0)</f>
+      <c r="J44" s="6" t="n">
+        <f aca="false">IFERROR(H44/D44,0)</f>
         <v>0.166671563181842</v>
       </c>
-      <c r="I44" s="6" t="n">
-        <f aca="false">IFERROR(D44/B44,0)</f>
+      <c r="K44" s="6" t="n">
+        <f aca="false">IFERROR(F44/D44,0)</f>
         <v>0.0932451383164095</v>
       </c>
-      <c r="J44" s="3" t="n">
+      <c r="L44" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A44)</f>
         <v>6</v>
       </c>
-      <c r="K44" s="4" t="n">
+      <c r="M44" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A44)</f>
         <v>2309.85215857614</v>
       </c>
-      <c r="L44" s="4" t="n">
+      <c r="N44" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A44)</f>
         <v>2103.755241</v>
       </c>
@@ -54860,47 +58683,53 @@
       <c r="A45" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B45" s="4" t="n">
+      <c r="B45" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="D45" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A45)</f>
         <v>64579.38</v>
       </c>
-      <c r="C45" s="5" t="n">
-        <f aca="false">B45/规则参数!$B$8</f>
+      <c r="E45" s="5" t="n">
+        <f aca="false">D45/规则参数!$B$8</f>
         <v>0.00197639199136181</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="F45" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A45)</f>
         <v>4849.17</v>
       </c>
-      <c r="E45" s="5" t="n">
-        <f aca="false">D45/规则参数!$B$9</f>
+      <c r="G45" s="5" t="n">
+        <f aca="false">F45/规则参数!$B$9</f>
         <v>0.00107780610902513</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A45)</f>
         <v>13029.07</v>
       </c>
-      <c r="G45" s="5" t="n">
-        <f aca="false">F45/规则参数!$B$10</f>
+      <c r="I45" s="5" t="n">
+        <f aca="false">H45/规则参数!$B$10</f>
         <v>0.00269099039590089</v>
       </c>
-      <c r="H45" s="6" t="n">
-        <f aca="false">IFERROR(F45/B45,0)</f>
+      <c r="J45" s="6" t="n">
+        <f aca="false">IFERROR(H45/D45,0)</f>
         <v>0.201752788583601</v>
       </c>
-      <c r="I45" s="6" t="n">
-        <f aca="false">IFERROR(D45/B45,0)</f>
+      <c r="K45" s="6" t="n">
+        <f aca="false">IFERROR(F45/D45,0)</f>
         <v>0.0750885189668901</v>
       </c>
-      <c r="J45" s="3" t="n">
+      <c r="L45" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A45)</f>
         <v>1</v>
       </c>
-      <c r="K45" s="4" t="n">
+      <c r="M45" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A45)</f>
         <v>567.189632072962</v>
       </c>
-      <c r="L45" s="4" t="n">
+      <c r="N45" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A45)</f>
         <v>497.039608</v>
       </c>
@@ -54909,47 +58738,53 @@
       <c r="A46" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="B46" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D46" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A46)</f>
         <v>158519.6</v>
       </c>
-      <c r="C46" s="5" t="n">
-        <f aca="false">B46/规则参数!$B$8</f>
+      <c r="E46" s="5" t="n">
+        <f aca="false">D46/规则参数!$B$8</f>
         <v>0.00485134524230299</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="F46" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A46)</f>
         <v>43497.82</v>
       </c>
-      <c r="E46" s="5" t="n">
-        <f aca="false">D46/规则参数!$B$9</f>
+      <c r="G46" s="5" t="n">
+        <f aca="false">F46/规则参数!$B$9</f>
         <v>0.00966809085374928</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A46)</f>
         <v>12962.33</v>
       </c>
-      <c r="G46" s="5" t="n">
-        <f aca="false">F46/规则参数!$B$10</f>
+      <c r="I46" s="5" t="n">
+        <f aca="false">H46/规则参数!$B$10</f>
         <v>0.00267720608903766</v>
       </c>
-      <c r="H46" s="6" t="n">
-        <f aca="false">IFERROR(F46/B46,0)</f>
+      <c r="J46" s="6" t="n">
+        <f aca="false">IFERROR(H46/D46,0)</f>
         <v>0.0817711500659855</v>
       </c>
-      <c r="I46" s="6" t="n">
-        <f aca="false">IFERROR(D46/B46,0)</f>
+      <c r="K46" s="6" t="n">
+        <f aca="false">IFERROR(F46/D46,0)</f>
         <v>0.274400263437455</v>
       </c>
-      <c r="J46" s="3" t="n">
+      <c r="L46" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A46)</f>
         <v>1</v>
       </c>
-      <c r="K46" s="4" t="n">
+      <c r="M46" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A46)</f>
         <v>19.3944813726504</v>
       </c>
-      <c r="L46" s="4" t="n">
+      <c r="N46" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A46)</f>
         <v>19.401324</v>
       </c>
@@ -54958,47 +58793,53 @@
       <c r="A47" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B47" s="4" t="n">
+      <c r="B47" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="D47" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A47)</f>
         <v>55678.72</v>
       </c>
-      <c r="C47" s="5" t="n">
-        <f aca="false">B47/规则参数!$B$8</f>
+      <c r="E47" s="5" t="n">
+        <f aca="false">D47/规则参数!$B$8</f>
         <v>0.00170399555240816</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="F47" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A47)</f>
         <v>-1195.17</v>
       </c>
-      <c r="E47" s="5" t="n">
-        <f aca="false">D47/规则参数!$B$9</f>
+      <c r="G47" s="5" t="n">
+        <f aca="false">F47/规则参数!$B$9</f>
         <v>-0.000265645775941772</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A47)</f>
         <v>12325.73</v>
       </c>
-      <c r="G47" s="5" t="n">
-        <f aca="false">F47/规则参数!$B$10</f>
+      <c r="I47" s="5" t="n">
+        <f aca="false">H47/规则参数!$B$10</f>
         <v>0.00254572437268872</v>
       </c>
-      <c r="H47" s="6" t="n">
-        <f aca="false">IFERROR(F47/B47,0)</f>
+      <c r="J47" s="6" t="n">
+        <f aca="false">IFERROR(H47/D47,0)</f>
         <v>0.221372366318766</v>
       </c>
-      <c r="I47" s="6" t="n">
-        <f aca="false">IFERROR(D47/B47,0)</f>
+      <c r="K47" s="6" t="n">
+        <f aca="false">IFERROR(F47/D47,0)</f>
         <v>-0.0214654719074002</v>
       </c>
-      <c r="J47" s="3" t="n">
+      <c r="L47" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A47)</f>
         <v>1</v>
       </c>
-      <c r="K47" s="4" t="n">
+      <c r="M47" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A47)</f>
         <v>1949.35192843514</v>
       </c>
-      <c r="L47" s="4" t="n">
+      <c r="N47" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A47)</f>
         <v>879.695424</v>
       </c>
@@ -55007,47 +58848,53 @@
       <c r="A48" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D48" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A48)</f>
         <v>108409.62</v>
       </c>
-      <c r="C48" s="5" t="n">
-        <f aca="false">B48/规则参数!$B$8</f>
+      <c r="E48" s="5" t="n">
+        <f aca="false">D48/规则参数!$B$8</f>
         <v>0.00331777580947009</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="F48" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A48)</f>
         <v>24869.73</v>
       </c>
-      <c r="E48" s="5" t="n">
-        <f aca="false">D48/规则参数!$B$9</f>
+      <c r="G48" s="5" t="n">
+        <f aca="false">F48/规则参数!$B$9</f>
         <v>0.00552769792022253</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A48)</f>
         <v>11375.95</v>
       </c>
-      <c r="G48" s="5" t="n">
-        <f aca="false">F48/规则参数!$B$10</f>
+      <c r="I48" s="5" t="n">
+        <f aca="false">H48/规则参数!$B$10</f>
         <v>0.0023495592697137</v>
       </c>
-      <c r="H48" s="6" t="n">
-        <f aca="false">IFERROR(F48/B48,0)</f>
+      <c r="J48" s="6" t="n">
+        <f aca="false">IFERROR(H48/D48,0)</f>
         <v>0.10493487570568</v>
       </c>
-      <c r="I48" s="6" t="n">
-        <f aca="false">IFERROR(D48/B48,0)</f>
+      <c r="K48" s="6" t="n">
+        <f aca="false">IFERROR(F48/D48,0)</f>
         <v>0.229405194852634</v>
       </c>
-      <c r="J48" s="3" t="n">
+      <c r="L48" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A48)</f>
         <v>2</v>
       </c>
-      <c r="K48" s="4" t="n">
+      <c r="M48" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A48)</f>
         <v>1015.22727715556</v>
       </c>
-      <c r="L48" s="4" t="n">
+      <c r="N48" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A48)</f>
         <v>991.519605</v>
       </c>
@@ -55056,47 +58903,53 @@
       <c r="A49" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B49" s="4" t="n">
+      <c r="B49" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="D49" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A49)</f>
         <v>72026.24</v>
       </c>
-      <c r="C49" s="5" t="n">
-        <f aca="false">B49/规则参数!$B$8</f>
+      <c r="E49" s="5" t="n">
+        <f aca="false">D49/规则参数!$B$8</f>
         <v>0.00220429623052905</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="F49" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A49)</f>
         <v>15040.52</v>
       </c>
-      <c r="E49" s="5" t="n">
-        <f aca="false">D49/规则参数!$B$9</f>
+      <c r="G49" s="5" t="n">
+        <f aca="false">F49/规则参数!$B$9</f>
         <v>0.00334299773753335</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A49)</f>
         <v>11112.4</v>
       </c>
-      <c r="G49" s="5" t="n">
-        <f aca="false">F49/规则参数!$B$10</f>
+      <c r="I49" s="5" t="n">
+        <f aca="false">H49/规则参数!$B$10</f>
         <v>0.00229512633483503</v>
       </c>
-      <c r="H49" s="6" t="n">
-        <f aca="false">IFERROR(F49/B49,0)</f>
+      <c r="J49" s="6" t="n">
+        <f aca="false">IFERROR(H49/D49,0)</f>
         <v>0.154282661430057</v>
       </c>
-      <c r="I49" s="6" t="n">
-        <f aca="false">IFERROR(D49/B49,0)</f>
+      <c r="K49" s="6" t="n">
+        <f aca="false">IFERROR(F49/D49,0)</f>
         <v>0.208820007819373</v>
       </c>
-      <c r="J49" s="3" t="n">
+      <c r="L49" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A49)</f>
         <v>1</v>
       </c>
-      <c r="K49" s="4" t="n">
+      <c r="M49" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A49)</f>
         <v>1907.59865354626</v>
       </c>
-      <c r="L49" s="4" t="n">
+      <c r="N49" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A49)</f>
         <v>1907.813033</v>
       </c>
@@ -55105,47 +58958,53 @@
       <c r="A50" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B50" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="D50" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A50)</f>
         <v>89857.68</v>
       </c>
-      <c r="C50" s="5" t="n">
-        <f aca="false">B50/规则参数!$B$8</f>
+      <c r="E50" s="5" t="n">
+        <f aca="false">D50/规则参数!$B$8</f>
         <v>0.00275001090308318</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="F50" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A50)</f>
         <v>14956.92</v>
       </c>
-      <c r="E50" s="5" t="n">
-        <f aca="false">D50/规则参数!$B$9</f>
+      <c r="G50" s="5" t="n">
+        <f aca="false">F50/规则参数!$B$9</f>
         <v>0.00332441629148908</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A50)</f>
         <v>11096.43</v>
       </c>
-      <c r="G50" s="5" t="n">
-        <f aca="false">F50/规则参数!$B$10</f>
+      <c r="I50" s="5" t="n">
+        <f aca="false">H50/规则参数!$B$10</f>
         <v>0.00229182793236866</v>
       </c>
-      <c r="H50" s="6" t="n">
-        <f aca="false">IFERROR(F50/B50,0)</f>
+      <c r="J50" s="6" t="n">
+        <f aca="false">IFERROR(H50/D50,0)</f>
         <v>0.123488943849875</v>
       </c>
-      <c r="I50" s="6" t="n">
-        <f aca="false">IFERROR(D50/B50,0)</f>
+      <c r="K50" s="6" t="n">
+        <f aca="false">IFERROR(F50/D50,0)</f>
         <v>0.166451214854423</v>
       </c>
-      <c r="J50" s="3" t="n">
+      <c r="L50" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A50)</f>
         <v>2</v>
       </c>
-      <c r="K50" s="4" t="n">
+      <c r="M50" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A50)</f>
         <v>701.904677135965</v>
       </c>
-      <c r="L50" s="4" t="n">
+      <c r="N50" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A50)</f>
         <v>701.846534</v>
       </c>
@@ -55154,47 +59013,53 @@
       <c r="A51" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B51" s="4" t="n">
+      <c r="B51" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="D51" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A51)</f>
         <v>90151.32</v>
       </c>
-      <c r="C51" s="5" t="n">
-        <f aca="false">B51/规则参数!$B$8</f>
+      <c r="E51" s="5" t="n">
+        <f aca="false">D51/规则参数!$B$8</f>
         <v>0.00275899748276765</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="F51" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A51)</f>
         <v>9088.06</v>
       </c>
-      <c r="E51" s="5" t="n">
-        <f aca="false">D51/规则参数!$B$9</f>
+      <c r="G51" s="5" t="n">
+        <f aca="false">F51/规则参数!$B$9</f>
         <v>0.00201996766192707</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A51)</f>
         <v>10425.69</v>
       </c>
-      <c r="G51" s="5" t="n">
-        <f aca="false">F51/规则参数!$B$10</f>
+      <c r="I51" s="5" t="n">
+        <f aca="false">H51/规则参数!$B$10</f>
         <v>0.00215329502878102</v>
       </c>
-      <c r="H51" s="6" t="n">
-        <f aca="false">IFERROR(F51/B51,0)</f>
+      <c r="J51" s="6" t="n">
+        <f aca="false">IFERROR(H51/D51,0)</f>
         <v>0.115646559584485</v>
       </c>
-      <c r="I51" s="6" t="n">
-        <f aca="false">IFERROR(D51/B51,0)</f>
+      <c r="K51" s="6" t="n">
+        <f aca="false">IFERROR(F51/D51,0)</f>
         <v>0.100808950994838</v>
       </c>
-      <c r="J51" s="3" t="n">
+      <c r="L51" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A51)</f>
         <v>3</v>
       </c>
-      <c r="K51" s="4" t="n">
+      <c r="M51" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A51)</f>
         <v>637.198671227297</v>
       </c>
-      <c r="L51" s="4" t="n">
+      <c r="N51" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A51)</f>
         <v>637.081297</v>
       </c>
@@ -55203,47 +59068,53 @@
       <c r="A52" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B52" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="D52" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A52)</f>
         <v>48241.85</v>
       </c>
-      <c r="C52" s="5" t="n">
-        <f aca="false">B52/规则参数!$B$8</f>
+      <c r="E52" s="5" t="n">
+        <f aca="false">D52/规则参数!$B$8</f>
         <v>0.00147639704791959</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="F52" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A52)</f>
         <v>5574.51</v>
       </c>
-      <c r="E52" s="5" t="n">
-        <f aca="false">D52/规则参数!$B$9</f>
+      <c r="G52" s="5" t="n">
+        <f aca="false">F52/规则参数!$B$9</f>
         <v>0.0012390246027303</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A52)</f>
         <v>9816.64</v>
       </c>
-      <c r="G52" s="5" t="n">
-        <f aca="false">F52/规则参数!$B$10</f>
+      <c r="I52" s="5" t="n">
+        <f aca="false">H52/规则参数!$B$10</f>
         <v>0.00202750341812704</v>
       </c>
-      <c r="H52" s="6" t="n">
-        <f aca="false">IFERROR(F52/B52,0)</f>
+      <c r="J52" s="6" t="n">
+        <f aca="false">IFERROR(H52/D52,0)</f>
         <v>0.203488050313162</v>
       </c>
-      <c r="I52" s="6" t="n">
-        <f aca="false">IFERROR(D52/B52,0)</f>
+      <c r="K52" s="6" t="n">
+        <f aca="false">IFERROR(F52/D52,0)</f>
         <v>0.11555340435742</v>
       </c>
-      <c r="J52" s="3" t="n">
+      <c r="L52" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A52)</f>
         <v>1</v>
       </c>
-      <c r="K52" s="4" t="n">
+      <c r="M52" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A52)</f>
         <v>1122.79618961545</v>
       </c>
-      <c r="L52" s="4" t="n">
+      <c r="N52" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A52)</f>
         <v>827.6625</v>
       </c>
@@ -55252,47 +59123,53 @@
       <c r="A53" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B53" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D53" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A53)</f>
         <v>49107.4</v>
       </c>
-      <c r="C53" s="5" t="n">
-        <f aca="false">B53/规则参数!$B$8</f>
+      <c r="E53" s="5" t="n">
+        <f aca="false">D53/规则参数!$B$8</f>
         <v>0.00150288640238727</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="F53" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A53)</f>
         <v>153.61</v>
       </c>
-      <c r="E53" s="5" t="n">
-        <f aca="false">D53/规则参数!$B$9</f>
+      <c r="G53" s="5" t="n">
+        <f aca="false">F53/规则参数!$B$9</f>
         <v>3.41422957758441E-005</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A53)</f>
         <v>9722.73</v>
       </c>
-      <c r="G53" s="5" t="n">
-        <f aca="false">F53/规则参数!$B$10</f>
+      <c r="I53" s="5" t="n">
+        <f aca="false">H53/规则参数!$B$10</f>
         <v>0.00200810748978534</v>
       </c>
-      <c r="H53" s="6" t="n">
-        <f aca="false">IFERROR(F53/B53,0)</f>
+      <c r="J53" s="6" t="n">
+        <f aca="false">IFERROR(H53/D53,0)</f>
         <v>0.197989101438887</v>
       </c>
-      <c r="I53" s="6" t="n">
-        <f aca="false">IFERROR(D53/B53,0)</f>
+      <c r="K53" s="6" t="n">
+        <f aca="false">IFERROR(F53/D53,0)</f>
         <v>0.00312804180225384</v>
       </c>
-      <c r="J53" s="3" t="n">
+      <c r="L53" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A53)</f>
         <v>2</v>
       </c>
-      <c r="K53" s="4" t="n">
+      <c r="M53" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A53)</f>
         <v>771.093238131276</v>
       </c>
-      <c r="L53" s="4" t="n">
+      <c r="N53" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A53)</f>
         <v>394.158672</v>
       </c>
@@ -55301,47 +59178,53 @@
       <c r="A54" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="D54" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A54)</f>
         <v>66049.51</v>
       </c>
-      <c r="C54" s="5" t="n">
-        <f aca="false">B54/规则参数!$B$8</f>
+      <c r="E54" s="5" t="n">
+        <f aca="false">D54/规则参数!$B$8</f>
         <v>0.00202138395564298</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="F54" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A54)</f>
         <v>8028.91</v>
       </c>
-      <c r="E54" s="5" t="n">
-        <f aca="false">D54/规则参数!$B$9</f>
+      <c r="G54" s="5" t="n">
+        <f aca="false">F54/规则参数!$B$9</f>
         <v>0.00178455452104441</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="H54" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A54)</f>
         <v>9674.15</v>
       </c>
-      <c r="G54" s="5" t="n">
-        <f aca="false">F54/规则参数!$B$10</f>
+      <c r="I54" s="5" t="n">
+        <f aca="false">H54/规则参数!$B$10</f>
         <v>0.00199807390232032</v>
       </c>
-      <c r="H54" s="6" t="n">
-        <f aca="false">IFERROR(F54/B54,0)</f>
+      <c r="J54" s="6" t="n">
+        <f aca="false">IFERROR(H54/D54,0)</f>
         <v>0.14646815699314</v>
       </c>
-      <c r="I54" s="6" t="n">
-        <f aca="false">IFERROR(D54/B54,0)</f>
+      <c r="K54" s="6" t="n">
+        <f aca="false">IFERROR(F54/D54,0)</f>
         <v>0.121558963874221</v>
       </c>
-      <c r="J54" s="3" t="n">
+      <c r="L54" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A54)</f>
         <v>2</v>
       </c>
-      <c r="K54" s="4" t="n">
+      <c r="M54" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A54)</f>
         <v>3324.36674495853</v>
       </c>
-      <c r="L54" s="4" t="n">
+      <c r="N54" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A54)</f>
         <v>3324.008442</v>
       </c>
@@ -55350,47 +59233,53 @@
       <c r="A55" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B55" s="4" t="n">
+      <c r="B55" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="D55" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A55)</f>
         <v>40365.34</v>
       </c>
-      <c r="C55" s="5" t="n">
-        <f aca="false">B55/规则参数!$B$8</f>
+      <c r="E55" s="5" t="n">
+        <f aca="false">D55/规则参数!$B$8</f>
         <v>0.00123534376924331</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="F55" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A55)</f>
         <v>-948.91</v>
       </c>
-      <c r="E55" s="5" t="n">
-        <f aca="false">D55/规则参数!$B$9</f>
+      <c r="G55" s="5" t="n">
+        <f aca="false">F55/规则参数!$B$9</f>
         <v>-0.000210910525907533</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A55)</f>
         <v>8795.92</v>
       </c>
-      <c r="G55" s="5" t="n">
-        <f aca="false">F55/规则参数!$B$10</f>
+      <c r="I55" s="5" t="n">
+        <f aca="false">H55/规则参数!$B$10</f>
         <v>0.00181668655115926</v>
       </c>
-      <c r="H55" s="6" t="n">
-        <f aca="false">IFERROR(F55/B55,0)</f>
+      <c r="J55" s="6" t="n">
+        <f aca="false">IFERROR(H55/D55,0)</f>
         <v>0.217907739659817</v>
       </c>
-      <c r="I55" s="6" t="n">
-        <f aca="false">IFERROR(D55/B55,0)</f>
+      <c r="K55" s="6" t="n">
+        <f aca="false">IFERROR(F55/D55,0)</f>
         <v>-0.0235080393228448</v>
       </c>
-      <c r="J55" s="3" t="n">
+      <c r="L55" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A55)</f>
         <v>2</v>
       </c>
-      <c r="K55" s="4" t="n">
+      <c r="M55" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A55)</f>
         <v>252.896045128424</v>
       </c>
-      <c r="L55" s="4" t="n">
+      <c r="N55" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A55)</f>
         <v>167.668038</v>
       </c>
@@ -55399,47 +59288,53 @@
       <c r="A56" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B56" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="D56" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A56)</f>
         <v>42098.53</v>
       </c>
-      <c r="C56" s="5" t="n">
-        <f aca="false">B56/规则参数!$B$8</f>
+      <c r="E56" s="5" t="n">
+        <f aca="false">D56/规则参数!$B$8</f>
         <v>0.00128838644068904</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="F56" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A56)</f>
         <v>512.18</v>
       </c>
-      <c r="E56" s="5" t="n">
-        <f aca="false">D56/规则参数!$B$9</f>
+      <c r="G56" s="5" t="n">
+        <f aca="false">F56/规则参数!$B$9</f>
         <v>0.000113840251614295</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="H56" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A56)</f>
         <v>8319.2</v>
       </c>
-      <c r="G56" s="5" t="n">
-        <f aca="false">F56/规则参数!$B$10</f>
+      <c r="I56" s="5" t="n">
+        <f aca="false">H56/规则参数!$B$10</f>
         <v>0.00171822603620816</v>
       </c>
-      <c r="H56" s="6" t="n">
-        <f aca="false">IFERROR(F56/B56,0)</f>
+      <c r="J56" s="6" t="n">
+        <f aca="false">IFERROR(H56/D56,0)</f>
         <v>0.197612600725013</v>
       </c>
-      <c r="I56" s="6" t="n">
-        <f aca="false">IFERROR(D56/B56,0)</f>
+      <c r="K56" s="6" t="n">
+        <f aca="false">IFERROR(F56/D56,0)</f>
         <v>0.0121662205307406</v>
       </c>
-      <c r="J56" s="3" t="n">
+      <c r="L56" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A56)</f>
         <v>2</v>
       </c>
-      <c r="K56" s="4" t="n">
+      <c r="M56" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A56)</f>
         <v>476.844322203258</v>
       </c>
-      <c r="L56" s="4" t="n">
+      <c r="N56" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A56)</f>
         <v>270.611663</v>
       </c>
@@ -55448,47 +59343,53 @@
       <c r="A57" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B57" s="4" t="n">
+      <c r="B57" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="D57" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A57)</f>
         <v>50443.79</v>
       </c>
-      <c r="C57" s="5" t="n">
-        <f aca="false">B57/规则参数!$B$8</f>
+      <c r="E57" s="5" t="n">
+        <f aca="false">D57/规则参数!$B$8</f>
         <v>0.0015437853780872</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="F57" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A57)</f>
         <v>-1591.8</v>
       </c>
-      <c r="E57" s="5" t="n">
-        <f aca="false">D57/规则参数!$B$9</f>
+      <c r="G57" s="5" t="n">
+        <f aca="false">F57/规则参数!$B$9</f>
         <v>-0.000353803179584588</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A57)</f>
         <v>8224.74</v>
       </c>
-      <c r="G57" s="5" t="n">
-        <f aca="false">F57/规则参数!$B$10</f>
+      <c r="I57" s="5" t="n">
+        <f aca="false">H57/规则参数!$B$10</f>
         <v>0.00169871651228997</v>
       </c>
-      <c r="H57" s="6" t="n">
-        <f aca="false">IFERROR(F57/B57,0)</f>
+      <c r="J57" s="6" t="n">
+        <f aca="false">IFERROR(H57/D57,0)</f>
         <v>0.163047621917386</v>
       </c>
-      <c r="I57" s="6" t="n">
-        <f aca="false">IFERROR(D57/B57,0)</f>
+      <c r="K57" s="6" t="n">
+        <f aca="false">IFERROR(F57/D57,0)</f>
         <v>-0.0315559160007605</v>
       </c>
-      <c r="J57" s="3" t="n">
+      <c r="L57" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A57)</f>
         <v>2</v>
       </c>
-      <c r="K57" s="4" t="n">
+      <c r="M57" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A57)</f>
         <v>172.472334370686</v>
       </c>
-      <c r="L57" s="4" t="n">
+      <c r="N57" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A57)</f>
         <v>120.587504</v>
       </c>
@@ -55497,47 +59398,53 @@
       <c r="A58" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B58" s="4" t="n">
+      <c r="B58" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D58" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A58)</f>
         <v>95627.52</v>
       </c>
-      <c r="C58" s="5" t="n">
-        <f aca="false">B58/规则参数!$B$8</f>
+      <c r="E58" s="5" t="n">
+        <f aca="false">D58/规则参数!$B$8</f>
         <v>0.00292659150152558</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="F58" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A58)</f>
         <v>20175.59</v>
       </c>
-      <c r="E58" s="5" t="n">
-        <f aca="false">D58/规则参数!$B$9</f>
+      <c r="G58" s="5" t="n">
+        <f aca="false">F58/规则参数!$B$9</f>
         <v>0.00448434972483668</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="H58" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A58)</f>
         <v>8038.56</v>
       </c>
-      <c r="G58" s="5" t="n">
-        <f aca="false">F58/规则参数!$B$10</f>
+      <c r="I58" s="5" t="n">
+        <f aca="false">H58/规则参数!$B$10</f>
         <v>0.0016602633769619</v>
       </c>
-      <c r="H58" s="6" t="n">
-        <f aca="false">IFERROR(F58/B58,0)</f>
+      <c r="J58" s="6" t="n">
+        <f aca="false">IFERROR(H58/D58,0)</f>
         <v>0.0840611572902863</v>
       </c>
-      <c r="I58" s="6" t="n">
-        <f aca="false">IFERROR(D58/B58,0)</f>
+      <c r="K58" s="6" t="n">
+        <f aca="false">IFERROR(F58/D58,0)</f>
         <v>0.210981002121565</v>
       </c>
-      <c r="J58" s="3" t="n">
+      <c r="L58" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A58)</f>
         <v>7</v>
       </c>
-      <c r="K58" s="4" t="n">
+      <c r="M58" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A58)</f>
         <v>895.478009534236</v>
       </c>
-      <c r="L58" s="4" t="n">
+      <c r="N58" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A58)</f>
         <v>1057.756323</v>
       </c>
@@ -55546,47 +59453,53 @@
       <c r="A59" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B59" s="4" t="n">
+      <c r="B59" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="D59" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A59)</f>
         <v>40206.1</v>
       </c>
-      <c r="C59" s="5" t="n">
-        <f aca="false">B59/规则参数!$B$8</f>
+      <c r="E59" s="5" t="n">
+        <f aca="false">D59/规则参数!$B$8</f>
         <v>0.00123047037682759</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="F59" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A59)</f>
         <v>2941.75</v>
       </c>
-      <c r="E59" s="5" t="n">
-        <f aca="false">D59/规则参数!$B$9</f>
+      <c r="G59" s="5" t="n">
+        <f aca="false">F59/规则参数!$B$9</f>
         <v>0.000653851302640384</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="H59" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A59)</f>
         <v>7172.28</v>
       </c>
-      <c r="G59" s="5" t="n">
-        <f aca="false">F59/规则参数!$B$10</f>
+      <c r="I59" s="5" t="n">
+        <f aca="false">H59/规则参数!$B$10</f>
         <v>0.0014813441478718</v>
       </c>
-      <c r="H59" s="6" t="n">
-        <f aca="false">IFERROR(F59/B59,0)</f>
+      <c r="J59" s="6" t="n">
+        <f aca="false">IFERROR(H59/D59,0)</f>
         <v>0.178387856569028</v>
       </c>
-      <c r="I59" s="6" t="n">
-        <f aca="false">IFERROR(D59/B59,0)</f>
+      <c r="K59" s="6" t="n">
+        <f aca="false">IFERROR(F59/D59,0)</f>
         <v>0.0731667582779728</v>
       </c>
-      <c r="J59" s="3" t="n">
+      <c r="L59" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A59)</f>
         <v>1</v>
       </c>
-      <c r="K59" s="4" t="n">
+      <c r="M59" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A59)</f>
         <v>1086.16441332037</v>
       </c>
-      <c r="L59" s="4" t="n">
+      <c r="N59" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A59)</f>
         <v>1086.238352</v>
       </c>
@@ -55595,47 +59508,53 @@
       <c r="A60" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="D60" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A60)</f>
         <v>25236.46</v>
       </c>
-      <c r="C60" s="5" t="n">
-        <f aca="false">B60/规则参数!$B$8</f>
+      <c r="E60" s="5" t="n">
+        <f aca="false">D60/规则参数!$B$8</f>
         <v>0.000772338437351404</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="F60" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A60)</f>
         <v>1219.31</v>
       </c>
-      <c r="E60" s="5" t="n">
-        <f aca="false">D60/规则参数!$B$9</f>
+      <c r="G60" s="5" t="n">
+        <f aca="false">F60/规则参数!$B$9</f>
         <v>0.000271011279620106</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="H60" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A60)</f>
         <v>6325.26</v>
       </c>
-      <c r="G60" s="5" t="n">
-        <f aca="false">F60/规则参数!$B$10</f>
+      <c r="I60" s="5" t="n">
+        <f aca="false">H60/规则参数!$B$10</f>
         <v>0.00130640282933287</v>
       </c>
-      <c r="H60" s="6" t="n">
-        <f aca="false">IFERROR(F60/B60,0)</f>
+      <c r="J60" s="6" t="n">
+        <f aca="false">IFERROR(H60/D60,0)</f>
         <v>0.250639748998077</v>
       </c>
-      <c r="I60" s="6" t="n">
-        <f aca="false">IFERROR(D60/B60,0)</f>
+      <c r="K60" s="6" t="n">
+        <f aca="false">IFERROR(F60/D60,0)</f>
         <v>0.0483154134930176</v>
       </c>
-      <c r="J60" s="3" t="n">
+      <c r="L60" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A60)</f>
         <v>1</v>
       </c>
-      <c r="K60" s="4" t="n">
+      <c r="M60" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A60)</f>
         <v>240.007610845578</v>
       </c>
-      <c r="L60" s="4" t="n">
+      <c r="N60" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A60)</f>
         <v>143.637</v>
       </c>
@@ -55644,47 +59563,53 @@
       <c r="A61" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B61" s="4" t="n">
+      <c r="B61" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="D61" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A61)</f>
         <v>13876.52</v>
       </c>
-      <c r="C61" s="5" t="n">
-        <f aca="false">B61/规则参数!$B$8</f>
+      <c r="E61" s="5" t="n">
+        <f aca="false">D61/规则参数!$B$8</f>
         <v>0.000424678016357108</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="F61" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A61)</f>
         <v>-405.1</v>
       </c>
-      <c r="E61" s="5" t="n">
-        <f aca="false">D61/规则参数!$B$9</f>
+      <c r="G61" s="5" t="n">
+        <f aca="false">F61/规则参数!$B$9</f>
         <v>-9.00399975183545E-005</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="H61" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A61)</f>
         <v>6194.22</v>
       </c>
-      <c r="G61" s="5" t="n">
-        <f aca="false">F61/规则参数!$B$10</f>
+      <c r="I61" s="5" t="n">
+        <f aca="false">H61/规则参数!$B$10</f>
         <v>0.00127933816689121</v>
       </c>
-      <c r="H61" s="6" t="n">
-        <f aca="false">IFERROR(F61/B61,0)</f>
+      <c r="J61" s="6" t="n">
+        <f aca="false">IFERROR(H61/D61,0)</f>
         <v>0.446381369392326</v>
       </c>
-      <c r="I61" s="6" t="n">
-        <f aca="false">IFERROR(D61/B61,0)</f>
+      <c r="K61" s="6" t="n">
+        <f aca="false">IFERROR(F61/D61,0)</f>
         <v>-0.0291931982946733</v>
       </c>
-      <c r="J61" s="3" t="n">
+      <c r="L61" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A61)</f>
         <v>1</v>
       </c>
-      <c r="K61" s="4" t="n">
+      <c r="M61" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A61)</f>
         <v>671.82628000392</v>
       </c>
-      <c r="L61" s="4" t="n">
+      <c r="N61" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A61)</f>
         <v>270.909</v>
       </c>
@@ -55693,47 +59618,53 @@
       <c r="A62" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B62" s="4" t="n">
+      <c r="B62" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="D62" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A62)</f>
         <v>35620.39</v>
       </c>
-      <c r="C62" s="5" t="n">
-        <f aca="false">B62/规则参数!$B$8</f>
+      <c r="E62" s="5" t="n">
+        <f aca="false">D62/规则参数!$B$8</f>
         <v>0.00109012897809152</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="F62" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A62)</f>
         <v>5611.58</v>
       </c>
-      <c r="E62" s="5" t="n">
-        <f aca="false">D62/规则参数!$B$9</f>
+      <c r="G62" s="5" t="n">
+        <f aca="false">F62/规则参数!$B$9</f>
         <v>0.00124726400709466</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="H62" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A62)</f>
         <v>6018.54</v>
       </c>
-      <c r="G62" s="5" t="n">
-        <f aca="false">F62/规则参数!$B$10</f>
+      <c r="I62" s="5" t="n">
+        <f aca="false">H62/规则参数!$B$10</f>
         <v>0.00124305367438699</v>
       </c>
-      <c r="H62" s="6" t="n">
-        <f aca="false">IFERROR(F62/B62,0)</f>
+      <c r="J62" s="6" t="n">
+        <f aca="false">IFERROR(H62/D62,0)</f>
         <v>0.168963338133019</v>
       </c>
-      <c r="I62" s="6" t="n">
-        <f aca="false">IFERROR(D62/B62,0)</f>
+      <c r="K62" s="6" t="n">
+        <f aca="false">IFERROR(F62/D62,0)</f>
         <v>0.157538421112178</v>
       </c>
-      <c r="J62" s="3" t="n">
+      <c r="L62" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A62)</f>
         <v>1</v>
       </c>
-      <c r="K62" s="4" t="n">
+      <c r="M62" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A62)</f>
         <v>699.927248949267</v>
       </c>
-      <c r="L62" s="4" t="n">
+      <c r="N62" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A62)</f>
         <v>700.07912</v>
       </c>
@@ -55742,47 +59673,53 @@
       <c r="A63" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B63" s="4" t="n">
+      <c r="B63" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="D63" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A63)</f>
         <v>116679.6</v>
       </c>
-      <c r="C63" s="5" t="n">
-        <f aca="false">B63/规则参数!$B$8</f>
+      <c r="E63" s="5" t="n">
+        <f aca="false">D63/规则参数!$B$8</f>
         <v>0.00357087087233261</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="F63" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A63)</f>
         <v>24799.3</v>
       </c>
-      <c r="E63" s="5" t="n">
-        <f aca="false">D63/规则参数!$B$9</f>
+      <c r="G63" s="5" t="n">
+        <f aca="false">F63/规则参数!$B$9</f>
         <v>0.00551204371872853</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="H63" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A63)</f>
         <v>5139.09</v>
       </c>
-      <c r="G63" s="5" t="n">
-        <f aca="false">F63/规则参数!$B$10</f>
+      <c r="I63" s="5" t="n">
+        <f aca="false">H63/规则参数!$B$10</f>
         <v>0.00106141434758354</v>
       </c>
-      <c r="H63" s="6" t="n">
-        <f aca="false">IFERROR(F63/B63,0)</f>
+      <c r="J63" s="6" t="n">
+        <f aca="false">IFERROR(H63/D63,0)</f>
         <v>0.0440444602141248</v>
       </c>
-      <c r="I63" s="6" t="n">
-        <f aca="false">IFERROR(D63/B63,0)</f>
+      <c r="K63" s="6" t="n">
+        <f aca="false">IFERROR(F63/D63,0)</f>
         <v>0.212541866787339</v>
       </c>
-      <c r="J63" s="3" t="n">
+      <c r="L63" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A63)</f>
         <v>5</v>
       </c>
-      <c r="K63" s="4" t="n">
+      <c r="M63" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A63)</f>
         <v>117.827180199264</v>
       </c>
-      <c r="L63" s="4" t="n">
+      <c r="N63" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A63)</f>
         <v>147.51031</v>
       </c>
@@ -55791,47 +59728,53 @@
       <c r="A64" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B64" s="4" t="n">
+      <c r="B64" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="D64" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A64)</f>
         <v>36106.43</v>
       </c>
-      <c r="C64" s="5" t="n">
-        <f aca="false">B64/规则参数!$B$8</f>
+      <c r="E64" s="5" t="n">
+        <f aca="false">D64/规则参数!$B$8</f>
         <v>0.00110500378121725</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="F64" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A64)</f>
         <v>5930.78</v>
       </c>
-      <c r="E64" s="5" t="n">
-        <f aca="false">D64/规则参数!$B$9</f>
+      <c r="G64" s="5" t="n">
+        <f aca="false">F64/规则参数!$B$9</f>
         <v>0.00131821134653643</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="H64" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A64)</f>
         <v>4316.76</v>
       </c>
-      <c r="G64" s="5" t="n">
-        <f aca="false">F64/规则参数!$B$10</f>
+      <c r="I64" s="5" t="n">
+        <f aca="false">H64/规则参数!$B$10</f>
         <v>0.000891572437741843</v>
       </c>
-      <c r="H64" s="6" t="n">
-        <f aca="false">IFERROR(F64/B64,0)</f>
+      <c r="J64" s="6" t="n">
+        <f aca="false">IFERROR(H64/D64,0)</f>
         <v>0.119556544360658</v>
       </c>
-      <c r="I64" s="6" t="n">
-        <f aca="false">IFERROR(D64/B64,0)</f>
+      <c r="K64" s="6" t="n">
+        <f aca="false">IFERROR(F64/D64,0)</f>
         <v>0.164258277542255</v>
       </c>
-      <c r="J64" s="3" t="n">
+      <c r="L64" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A64)</f>
         <v>1</v>
       </c>
-      <c r="K64" s="4" t="n">
+      <c r="M64" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A64)</f>
         <v>100.21109991766</v>
       </c>
-      <c r="L64" s="4" t="n">
+      <c r="N64" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A64)</f>
         <v>100.247524</v>
       </c>
@@ -55840,47 +59783,53 @@
       <c r="A65" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="B65" s="4" t="n">
+      <c r="B65" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="D65" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A65)</f>
         <v>59313.98</v>
       </c>
-      <c r="C65" s="5" t="n">
-        <f aca="false">B65/规则参数!$B$8</f>
+      <c r="E65" s="5" t="n">
+        <f aca="false">D65/规则参数!$B$8</f>
         <v>0.00181524931096883</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="F65" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A65)</f>
         <v>16937.19</v>
       </c>
-      <c r="E65" s="5" t="n">
-        <f aca="false">D65/规则参数!$B$9</f>
+      <c r="G65" s="5" t="n">
+        <f aca="false">F65/规则参数!$B$9</f>
         <v>0.00376456318333226</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="H65" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A65)</f>
         <v>3896.88</v>
       </c>
-      <c r="G65" s="5" t="n">
-        <f aca="false">F65/规则参数!$B$10</f>
+      <c r="I65" s="5" t="n">
+        <f aca="false">H65/规则参数!$B$10</f>
         <v>0.000804851509277197</v>
       </c>
-      <c r="H65" s="6" t="n">
-        <f aca="false">IFERROR(F65/B65,0)</f>
+      <c r="J65" s="6" t="n">
+        <f aca="false">IFERROR(H65/D65,0)</f>
         <v>0.0656991825535902</v>
       </c>
-      <c r="I65" s="6" t="n">
-        <f aca="false">IFERROR(D65/B65,0)</f>
+      <c r="K65" s="6" t="n">
+        <f aca="false">IFERROR(F65/D65,0)</f>
         <v>0.285551399518292</v>
       </c>
-      <c r="J65" s="3" t="n">
+      <c r="L65" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A65)</f>
         <v>11</v>
       </c>
-      <c r="K65" s="4" t="n">
+      <c r="M65" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A65)</f>
         <v>64.9197414333841</v>
       </c>
-      <c r="L65" s="4" t="n">
+      <c r="N65" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A65)</f>
         <v>64.965108</v>
       </c>
@@ -55889,47 +59838,53 @@
       <c r="A66" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="D66" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A66)</f>
         <v>31340.99</v>
       </c>
-      <c r="C66" s="5" t="n">
-        <f aca="false">B66/规则参数!$B$8</f>
+      <c r="E66" s="5" t="n">
+        <f aca="false">D66/规则参数!$B$8</f>
         <v>0.000959161912631407</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="F66" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A66)</f>
         <v>7149.91</v>
       </c>
-      <c r="E66" s="5" t="n">
-        <f aca="false">D66/规则参数!$B$9</f>
+      <c r="G66" s="5" t="n">
+        <f aca="false">F66/规则参数!$B$9</f>
         <v>0.00158918261825835</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="H66" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A66)</f>
         <v>3892.52</v>
       </c>
-      <c r="G66" s="5" t="n">
-        <f aca="false">F66/规则参数!$B$10</f>
+      <c r="I66" s="5" t="n">
+        <f aca="false">H66/规则参数!$B$10</f>
         <v>0.000803951006161769</v>
       </c>
-      <c r="H66" s="6" t="n">
-        <f aca="false">IFERROR(F66/B66,0)</f>
+      <c r="J66" s="6" t="n">
+        <f aca="false">IFERROR(H66/D66,0)</f>
         <v>0.124199012220099</v>
       </c>
-      <c r="I66" s="6" t="n">
-        <f aca="false">IFERROR(D66/B66,0)</f>
+      <c r="K66" s="6" t="n">
+        <f aca="false">IFERROR(F66/D66,0)</f>
         <v>0.228132870084831</v>
       </c>
-      <c r="J66" s="3" t="n">
+      <c r="L66" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A66)</f>
         <v>1</v>
       </c>
-      <c r="K66" s="4" t="n">
+      <c r="M66" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A66)</f>
         <v>391.573403737406</v>
       </c>
-      <c r="L66" s="4" t="n">
+      <c r="N66" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A66)</f>
         <v>391.576518</v>
       </c>
@@ -55938,47 +59893,53 @@
       <c r="A67" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B67" s="4" t="n">
+      <c r="B67" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D67" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A67)</f>
         <v>12610.83</v>
       </c>
-      <c r="C67" s="5" t="n">
-        <f aca="false">B67/规则参数!$B$8</f>
+      <c r="E67" s="5" t="n">
+        <f aca="false">D67/规则参数!$B$8</f>
         <v>0.000385942748543346</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="F67" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A67)</f>
         <v>-4244.5</v>
       </c>
-      <c r="E67" s="5" t="n">
-        <f aca="false">D67/规则参数!$B$9</f>
+      <c r="G67" s="5" t="n">
+        <f aca="false">F67/规则参数!$B$9</f>
         <v>-0.0009434084657286</v>
       </c>
-      <c r="F67" s="4" t="n">
+      <c r="H67" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A67)</f>
         <v>3703.5</v>
       </c>
-      <c r="G67" s="5" t="n">
-        <f aca="false">F67/规则参数!$B$10</f>
+      <c r="I67" s="5" t="n">
+        <f aca="false">H67/规则参数!$B$10</f>
         <v>0.000764911304584206</v>
       </c>
-      <c r="H67" s="6" t="n">
-        <f aca="false">IFERROR(F67/B67,0)</f>
+      <c r="J67" s="6" t="n">
+        <f aca="false">IFERROR(H67/D67,0)</f>
         <v>0.293676149785541</v>
       </c>
-      <c r="I67" s="6" t="n">
-        <f aca="false">IFERROR(D67/B67,0)</f>
+      <c r="K67" s="6" t="n">
+        <f aca="false">IFERROR(F67/D67,0)</f>
         <v>-0.336575784464623</v>
       </c>
-      <c r="J67" s="3" t="n">
+      <c r="L67" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A67)</f>
         <v>1</v>
       </c>
-      <c r="K67" s="4" t="n">
+      <c r="M67" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A67)</f>
         <v>117.446965822234</v>
       </c>
-      <c r="L67" s="4" t="n">
+      <c r="N67" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A67)</f>
         <v>0</v>
       </c>
@@ -55987,47 +59948,53 @@
       <c r="A68" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="B68" s="4" t="n">
+      <c r="B68" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="D68" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A68)</f>
         <v>3206.27</v>
       </c>
-      <c r="C68" s="5" t="n">
-        <f aca="false">B68/规则参数!$B$8</f>
+      <c r="E68" s="5" t="n">
+        <f aca="false">D68/规则参数!$B$8</f>
         <v>9.81249177391238E-005</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="F68" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A68)</f>
         <v>-3102.23</v>
       </c>
-      <c r="E68" s="5" t="n">
-        <f aca="false">D68/规则参数!$B$9</f>
+      <c r="G68" s="5" t="n">
+        <f aca="false">F68/规则参数!$B$9</f>
         <v>-0.000689520566530153</v>
       </c>
-      <c r="F68" s="4" t="n">
+      <c r="H68" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A68)</f>
         <v>3603.12</v>
       </c>
-      <c r="G68" s="5" t="n">
-        <f aca="false">F68/规则参数!$B$10</f>
+      <c r="I68" s="5" t="n">
+        <f aca="false">H68/规则参数!$B$10</f>
         <v>0.000744179079188185</v>
       </c>
-      <c r="H68" s="6" t="n">
-        <f aca="false">IFERROR(F68/B68,0)</f>
+      <c r="J68" s="6" t="n">
+        <f aca="false">IFERROR(H68/D68,0)</f>
         <v>1.12377310706834</v>
       </c>
-      <c r="I68" s="6" t="n">
-        <f aca="false">IFERROR(D68/B68,0)</f>
+      <c r="K68" s="6" t="n">
+        <f aca="false">IFERROR(F68/D68,0)</f>
         <v>-0.967551079603402</v>
       </c>
-      <c r="J68" s="3" t="n">
+      <c r="L68" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A68)</f>
         <v>2</v>
       </c>
-      <c r="K68" s="4" t="n">
+      <c r="M68" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A68)</f>
         <v>14.3851567812713</v>
       </c>
-      <c r="L68" s="4" t="n">
+      <c r="N68" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A68)</f>
         <v>1.370752</v>
       </c>
@@ -56036,47 +60003,53 @@
       <c r="A69" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="B69" s="4" t="n">
+      <c r="B69" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="D69" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A69)</f>
         <v>29907.88</v>
       </c>
-      <c r="C69" s="5" t="n">
-        <f aca="false">B69/规则参数!$B$8</f>
+      <c r="E69" s="5" t="n">
+        <f aca="false">D69/规则参数!$B$8</f>
         <v>0.000915302911093447</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="F69" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A69)</f>
         <v>4431.21</v>
       </c>
-      <c r="E69" s="5" t="n">
-        <f aca="false">D69/规则参数!$B$9</f>
+      <c r="G69" s="5" t="n">
+        <f aca="false">F69/规则参数!$B$9</f>
         <v>0.00098490776944781</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="H69" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A69)</f>
         <v>2573.34</v>
       </c>
-      <c r="G69" s="5" t="n">
-        <f aca="false">F69/规则参数!$B$10</f>
+      <c r="I69" s="5" t="n">
+        <f aca="false">H69/规则参数!$B$10</f>
         <v>0.000531490983269534</v>
       </c>
-      <c r="H69" s="6" t="n">
-        <f aca="false">IFERROR(F69/B69,0)</f>
+      <c r="J69" s="6" t="n">
+        <f aca="false">IFERROR(H69/D69,0)</f>
         <v>0.0860422069367672</v>
       </c>
-      <c r="I69" s="6" t="n">
-        <f aca="false">IFERROR(D69/B69,0)</f>
+      <c r="K69" s="6" t="n">
+        <f aca="false">IFERROR(F69/D69,0)</f>
         <v>0.148161955979494</v>
       </c>
-      <c r="J69" s="3" t="n">
+      <c r="L69" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A69)</f>
         <v>6</v>
       </c>
-      <c r="K69" s="4" t="n">
+      <c r="M69" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A69)</f>
         <v>282.495153919312</v>
       </c>
-      <c r="L69" s="4" t="n">
+      <c r="N69" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A69)</f>
         <v>282.58432</v>
       </c>
@@ -56085,47 +60058,53 @@
       <c r="A70" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B70" s="4" t="n">
+      <c r="B70" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="D70" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A70)</f>
         <v>21835.03</v>
       </c>
-      <c r="C70" s="5" t="n">
-        <f aca="false">B70/规则参数!$B$8</f>
+      <c r="E70" s="5" t="n">
+        <f aca="false">D70/规则参数!$B$8</f>
         <v>0.000668240828932467</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="F70" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A70)</f>
         <v>4856.89</v>
       </c>
-      <c r="E70" s="5" t="n">
-        <f aca="false">D70/规则参数!$B$9</f>
+      <c r="G70" s="5" t="n">
+        <f aca="false">F70/规则参数!$B$9</f>
         <v>0.00107952200332491</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="H70" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A70)</f>
         <v>2288.1</v>
       </c>
-      <c r="G70" s="5" t="n">
-        <f aca="false">F70/规则参数!$B$10</f>
+      <c r="I70" s="5" t="n">
+        <f aca="false">H70/规则参数!$B$10</f>
         <v>0.000472578251929019</v>
       </c>
-      <c r="H70" s="6" t="n">
-        <f aca="false">IFERROR(F70/B70,0)</f>
+      <c r="J70" s="6" t="n">
+        <f aca="false">IFERROR(H70/D70,0)</f>
         <v>0.104790330033895</v>
       </c>
-      <c r="I70" s="6" t="n">
-        <f aca="false">IFERROR(D70/B70,0)</f>
+      <c r="K70" s="6" t="n">
+        <f aca="false">IFERROR(F70/D70,0)</f>
         <v>0.222435691638619</v>
       </c>
-      <c r="J70" s="3" t="n">
+      <c r="L70" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A70)</f>
         <v>1</v>
       </c>
-      <c r="K70" s="4" t="n">
+      <c r="M70" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A70)</f>
         <v>1357.03267813234</v>
       </c>
-      <c r="L70" s="4" t="n">
+      <c r="N70" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A70)</f>
         <v>1357.157904</v>
       </c>
@@ -56134,47 +60113,53 @@
       <c r="A71" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="B71" s="4" t="n">
+      <c r="B71" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="D71" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A71)</f>
         <v>12171.45</v>
       </c>
-      <c r="C71" s="5" t="n">
-        <f aca="false">B71/规则参数!$B$8</f>
+      <c r="E71" s="5" t="n">
+        <f aca="false">D71/规则参数!$B$8</f>
         <v>0.000372495931414341</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="F71" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A71)</f>
         <v>1890.16</v>
       </c>
-      <c r="E71" s="5" t="n">
-        <f aca="false">D71/规则参数!$B$9</f>
+      <c r="G71" s="5" t="n">
+        <f aca="false">F71/规则参数!$B$9</f>
         <v>0.000420118493481345</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="H71" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A71)</f>
         <v>2146.34</v>
       </c>
-      <c r="G71" s="5" t="n">
-        <f aca="false">F71/规则参数!$B$10</f>
+      <c r="I71" s="5" t="n">
+        <f aca="false">H71/规则参数!$B$10</f>
         <v>0.000443299508432905</v>
       </c>
-      <c r="H71" s="6" t="n">
-        <f aca="false">IFERROR(F71/B71,0)</f>
+      <c r="J71" s="6" t="n">
+        <f aca="false">IFERROR(H71/D71,0)</f>
         <v>0.17634217780133</v>
       </c>
-      <c r="I71" s="6" t="n">
-        <f aca="false">IFERROR(D71/B71,0)</f>
+      <c r="K71" s="6" t="n">
+        <f aca="false">IFERROR(F71/D71,0)</f>
         <v>0.155294562274832</v>
       </c>
-      <c r="J71" s="3" t="n">
+      <c r="L71" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A71)</f>
         <v>1</v>
       </c>
-      <c r="K71" s="4" t="n">
+      <c r="M71" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A71)</f>
         <v>737.4118483336</v>
       </c>
-      <c r="L71" s="4" t="n">
+      <c r="N71" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A71)</f>
         <v>627.2565</v>
       </c>
@@ -56183,47 +60168,53 @@
       <c r="A72" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="B72" s="4" t="n">
+      <c r="B72" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D72" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A72)</f>
         <v>9658.08</v>
       </c>
-      <c r="C72" s="5" t="n">
-        <f aca="false">B72/规则参数!$B$8</f>
+      <c r="E72" s="5" t="n">
+        <f aca="false">D72/规则参数!$B$8</f>
         <v>0.000295576575122456</v>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="F72" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A72)</f>
         <v>-2808.95</v>
       </c>
-      <c r="E72" s="5" t="n">
-        <f aca="false">D72/规则参数!$B$9</f>
+      <c r="G72" s="5" t="n">
+        <f aca="false">F72/规则参数!$B$9</f>
         <v>-0.000624334364426517</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="H72" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A72)</f>
         <v>1375.84</v>
       </c>
-      <c r="G72" s="5" t="n">
-        <f aca="false">F72/规则参数!$B$10</f>
+      <c r="I72" s="5" t="n">
+        <f aca="false">H72/规则参数!$B$10</f>
         <v>0.000284162432644561</v>
       </c>
-      <c r="H72" s="6" t="n">
-        <f aca="false">IFERROR(F72/B72,0)</f>
+      <c r="J72" s="6" t="n">
+        <f aca="false">IFERROR(H72/D72,0)</f>
         <v>0.142454815035701</v>
       </c>
-      <c r="I72" s="6" t="n">
-        <f aca="false">IFERROR(D72/B72,0)</f>
+      <c r="K72" s="6" t="n">
+        <f aca="false">IFERROR(F72/D72,0)</f>
         <v>-0.290839380083826</v>
       </c>
-      <c r="J72" s="3" t="n">
+      <c r="L72" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A72)</f>
         <v>2</v>
       </c>
-      <c r="K72" s="4" t="n">
+      <c r="M72" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A72)</f>
         <v>0</v>
       </c>
-      <c r="L72" s="4" t="n">
+      <c r="N72" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A72)</f>
         <v>0</v>
       </c>
@@ -56232,47 +60223,53 @@
       <c r="A73" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="B73" s="4" t="n">
+      <c r="B73" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D73" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A73)</f>
         <v>9237.73</v>
       </c>
-      <c r="C73" s="5" t="n">
-        <f aca="false">B73/规则参数!$B$8</f>
+      <c r="E73" s="5" t="n">
+        <f aca="false">D73/规则参数!$B$8</f>
         <v>0.000282712153482469</v>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="F73" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A73)</f>
         <v>1010.49</v>
       </c>
-      <c r="E73" s="5" t="n">
-        <f aca="false">D73/规则参数!$B$9</f>
+      <c r="G73" s="5" t="n">
+        <f aca="false">F73/规则参数!$B$9</f>
         <v>0.000224597672407608</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="H73" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A73)</f>
         <v>1124.37</v>
       </c>
-      <c r="G73" s="5" t="n">
-        <f aca="false">F73/规则参数!$B$10</f>
+      <c r="I73" s="5" t="n">
+        <f aca="false">H73/规则参数!$B$10</f>
         <v>0.000232224469700376</v>
       </c>
-      <c r="H73" s="6" t="n">
-        <f aca="false">IFERROR(F73/B73,0)</f>
+      <c r="J73" s="6" t="n">
+        <f aca="false">IFERROR(H73/D73,0)</f>
         <v>0.12171496677214</v>
       </c>
-      <c r="I73" s="6" t="n">
-        <f aca="false">IFERROR(D73/B73,0)</f>
+      <c r="K73" s="6" t="n">
+        <f aca="false">IFERROR(F73/D73,0)</f>
         <v>0.109387262888177</v>
       </c>
-      <c r="J73" s="3" t="n">
+      <c r="L73" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A73)</f>
         <v>6</v>
       </c>
-      <c r="K73" s="4" t="n">
+      <c r="M73" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A73)</f>
         <v>0</v>
       </c>
-      <c r="L73" s="4" t="n">
+      <c r="N73" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A73)</f>
         <v>0</v>
       </c>
@@ -56281,47 +60278,53 @@
       <c r="A74" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B74" s="4" t="n">
+      <c r="B74" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D74" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A74)</f>
         <v>15297.97</v>
       </c>
-      <c r="C74" s="5" t="n">
-        <f aca="false">B74/规则参数!$B$8</f>
+      <c r="E74" s="5" t="n">
+        <f aca="false">D74/规则参数!$B$8</f>
         <v>0.000468180174416248</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="F74" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A74)</f>
         <v>-8689.65</v>
       </c>
-      <c r="E74" s="5" t="n">
-        <f aca="false">D74/规则参数!$B$9</f>
+      <c r="G74" s="5" t="n">
+        <f aca="false">F74/规则参数!$B$9</f>
         <v>-0.00193141462462446</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="H74" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A74)</f>
         <v>987.72</v>
       </c>
-      <c r="G74" s="5" t="n">
-        <f aca="false">F74/规则参数!$B$10</f>
+      <c r="I74" s="5" t="n">
+        <f aca="false">H74/规则参数!$B$10</f>
         <v>0.000204001132378537</v>
       </c>
-      <c r="H74" s="6" t="n">
-        <f aca="false">IFERROR(F74/B74,0)</f>
+      <c r="J74" s="6" t="n">
+        <f aca="false">IFERROR(H74/D74,0)</f>
         <v>0.0645654292693736</v>
       </c>
-      <c r="I74" s="6" t="n">
-        <f aca="false">IFERROR(D74/B74,0)</f>
+      <c r="K74" s="6" t="n">
+        <f aca="false">IFERROR(F74/D74,0)</f>
         <v>-0.568026345979238</v>
       </c>
-      <c r="J74" s="3" t="n">
+      <c r="L74" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A74)</f>
         <v>3</v>
       </c>
-      <c r="K74" s="4" t="n">
+      <c r="M74" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A74)</f>
         <v>0</v>
       </c>
-      <c r="L74" s="4" t="n">
+      <c r="N74" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A74)</f>
         <v>0</v>
       </c>
@@ -56330,47 +60333,53 @@
       <c r="A75" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="B75" s="4" t="n">
+      <c r="B75" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D75" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A75)</f>
         <v>3106.5</v>
       </c>
-      <c r="C75" s="5" t="n">
-        <f aca="false">B75/规则参数!$B$8</f>
+      <c r="E75" s="5" t="n">
+        <f aca="false">D75/规则参数!$B$8</f>
         <v>9.50715494816681E-005</v>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="F75" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A75)</f>
         <v>335.39</v>
       </c>
-      <c r="E75" s="5" t="n">
-        <f aca="false">D75/规则参数!$B$9</f>
+      <c r="G75" s="5" t="n">
+        <f aca="false">F75/规则参数!$B$9</f>
         <v>7.45458276170845E-005</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="H75" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A75)</f>
         <v>703.26</v>
       </c>
-      <c r="G75" s="5" t="n">
-        <f aca="false">F75/规则参数!$B$10</f>
+      <c r="I75" s="5" t="n">
+        <f aca="false">H75/规则参数!$B$10</f>
         <v>0.000145249500219222</v>
       </c>
-      <c r="H75" s="6" t="n">
-        <f aca="false">IFERROR(F75/B75,0)</f>
+      <c r="J75" s="6" t="n">
+        <f aca="false">IFERROR(H75/D75,0)</f>
         <v>0.226383389666828</v>
       </c>
-      <c r="I75" s="6" t="n">
-        <f aca="false">IFERROR(D75/B75,0)</f>
+      <c r="K75" s="6" t="n">
+        <f aca="false">IFERROR(F75/D75,0)</f>
         <v>0.107963946563657</v>
       </c>
-      <c r="J75" s="3" t="n">
+      <c r="L75" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A75)</f>
         <v>1</v>
       </c>
-      <c r="K75" s="4" t="n">
+      <c r="M75" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A75)</f>
         <v>431.160748623853</v>
       </c>
-      <c r="L75" s="4" t="n">
+      <c r="N75" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A75)</f>
         <v>342.8208</v>
       </c>
@@ -56379,47 +60388,53 @@
       <c r="A76" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="B76" s="4" t="n">
+      <c r="B76" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D76" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A76)</f>
         <v>4376.11</v>
       </c>
-      <c r="C76" s="5" t="n">
-        <f aca="false">B76/规则参数!$B$8</f>
+      <c r="E76" s="5" t="n">
+        <f aca="false">D76/规则参数!$B$8</f>
         <v>0.000133926785257435</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="F76" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A76)</f>
         <v>272.35</v>
       </c>
-      <c r="E76" s="5" t="n">
-        <f aca="false">D76/规则参数!$B$9</f>
+      <c r="G76" s="5" t="n">
+        <f aca="false">F76/规则参数!$B$9</f>
         <v>6.0534172609538E-005</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="H76" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A76)</f>
         <v>87.85</v>
       </c>
-      <c r="G76" s="5" t="n">
-        <f aca="false">F76/规则参数!$B$10</f>
+      <c r="I76" s="5" t="n">
+        <f aca="false">H76/规则参数!$B$10</f>
         <v>1.81443116262245E-005</v>
       </c>
-      <c r="H76" s="6" t="n">
-        <f aca="false">IFERROR(F76/B76,0)</f>
+      <c r="J76" s="6" t="n">
+        <f aca="false">IFERROR(H76/D76,0)</f>
         <v>0.0200749067093834</v>
       </c>
-      <c r="I76" s="6" t="n">
-        <f aca="false">IFERROR(D76/B76,0)</f>
+      <c r="K76" s="6" t="n">
+        <f aca="false">IFERROR(F76/D76,0)</f>
         <v>0.0622356385008604</v>
       </c>
-      <c r="J76" s="3" t="n">
+      <c r="L76" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A76)</f>
         <v>3</v>
       </c>
-      <c r="K76" s="4" t="n">
+      <c r="M76" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A76)</f>
         <v>0</v>
       </c>
-      <c r="L76" s="4" t="n">
+      <c r="N76" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A76)</f>
         <v>0</v>
       </c>
@@ -56428,47 +60443,53 @@
       <c r="A77" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="B77" s="4" t="n">
+      <c r="B77" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D77" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A77)</f>
         <v>543.53</v>
       </c>
-      <c r="C77" s="5" t="n">
-        <f aca="false">B77/规则参数!$B$8</f>
+      <c r="E77" s="5" t="n">
+        <f aca="false">D77/规则参数!$B$8</f>
         <v>1.66342312215584E-005</v>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="F77" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A77)</f>
         <v>-1617.93</v>
       </c>
-      <c r="E77" s="5" t="n">
-        <f aca="false">D77/规则参数!$B$9</f>
+      <c r="G77" s="5" t="n">
+        <f aca="false">F77/规则参数!$B$9</f>
         <v>-0.000359610992803928</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="H77" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A77)</f>
         <v>27.59</v>
       </c>
-      <c r="G77" s="5" t="n">
-        <f aca="false">F77/规则参数!$B$10</f>
+      <c r="I77" s="5" t="n">
+        <f aca="false">H77/规则参数!$B$10</f>
         <v>5.69836719143465E-006</v>
       </c>
-      <c r="H77" s="6" t="n">
-        <f aca="false">IFERROR(F77/B77,0)</f>
+      <c r="J77" s="6" t="n">
+        <f aca="false">IFERROR(H77/D77,0)</f>
         <v>0.0507607675749269</v>
       </c>
-      <c r="I77" s="6" t="n">
-        <f aca="false">IFERROR(D77/B77,0)</f>
+      <c r="K77" s="6" t="n">
+        <f aca="false">IFERROR(F77/D77,0)</f>
         <v>-2.97670781741578</v>
       </c>
-      <c r="J77" s="3" t="n">
+      <c r="L77" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A77)</f>
         <v>4</v>
       </c>
-      <c r="K77" s="4" t="n">
+      <c r="M77" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A77)</f>
         <v>0</v>
       </c>
-      <c r="L77" s="4" t="n">
+      <c r="N77" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A77)</f>
         <v>0</v>
       </c>
@@ -56477,47 +60498,53 @@
       <c r="A78" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B78" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D78" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A78)</f>
         <v>0</v>
       </c>
-      <c r="C78" s="5" t="n">
-        <f aca="false">B78/规则参数!$B$8</f>
-        <v>0</v>
-      </c>
-      <c r="D78" s="4" t="n">
+      <c r="E78" s="5" t="n">
+        <f aca="false">D78/规则参数!$B$8</f>
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A78)</f>
         <v>-0.81</v>
       </c>
-      <c r="E78" s="5" t="n">
-        <f aca="false">D78/规则参数!$B$9</f>
+      <c r="G78" s="5" t="n">
+        <f aca="false">F78/规则参数!$B$9</f>
         <v>-1.80035541816507E-007</v>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="H78" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A78)</f>
         <v>0.75</v>
       </c>
-      <c r="G78" s="5" t="n">
-        <f aca="false">F78/规则参数!$B$10</f>
+      <c r="I78" s="5" t="n">
+        <f aca="false">H78/规则参数!$B$10</f>
         <v>1.54903058846538E-007</v>
       </c>
-      <c r="H78" s="6" t="n">
-        <f aca="false">IFERROR(F78/B78,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I78" s="6" t="n">
-        <f aca="false">IFERROR(D78/B78,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="n">
+      <c r="J78" s="6" t="n">
+        <f aca="false">IFERROR(H78/D78,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K78" s="6" t="n">
+        <f aca="false">IFERROR(F78/D78,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L78" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A78)</f>
         <v>1</v>
       </c>
-      <c r="K78" s="4" t="n">
+      <c r="M78" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A78)</f>
         <v>0</v>
       </c>
-      <c r="L78" s="4" t="n">
+      <c r="N78" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A78)</f>
         <v>0</v>
       </c>
@@ -56526,47 +60553,53 @@
       <c r="A79" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="B79" s="4" t="n">
+      <c r="B79" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D79" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A79)</f>
         <v>32.47</v>
       </c>
-      <c r="C79" s="5" t="n">
-        <f aca="false">B79/规则参数!$B$8</f>
+      <c r="E79" s="5" t="n">
+        <f aca="false">D79/规则参数!$B$8</f>
         <v>9.93714215892407E-007</v>
       </c>
-      <c r="D79" s="4" t="n">
+      <c r="F79" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A79)</f>
         <v>8.82</v>
       </c>
-      <c r="E79" s="5" t="n">
-        <f aca="false">D79/规则参数!$B$9</f>
+      <c r="G79" s="5" t="n">
+        <f aca="false">F79/规则参数!$B$9</f>
         <v>1.96038701089086E-006</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="H79" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A79)</f>
         <v>0</v>
       </c>
-      <c r="G79" s="5" t="n">
-        <f aca="false">F79/规则参数!$B$10</f>
-        <v>0</v>
-      </c>
-      <c r="H79" s="6" t="n">
-        <f aca="false">IFERROR(F79/B79,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I79" s="6" t="n">
-        <f aca="false">IFERROR(D79/B79,0)</f>
+      <c r="I79" s="5" t="n">
+        <f aca="false">H79/规则参数!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="J79" s="6" t="n">
+        <f aca="false">IFERROR(H79/D79,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K79" s="6" t="n">
+        <f aca="false">IFERROR(F79/D79,0)</f>
         <v>0.271635355712966</v>
       </c>
-      <c r="J79" s="3" t="n">
+      <c r="L79" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A79)</f>
         <v>1</v>
       </c>
-      <c r="K79" s="4" t="n">
+      <c r="M79" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A79)</f>
         <v>0</v>
       </c>
-      <c r="L79" s="4" t="n">
+      <c r="N79" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A79)</f>
         <v>0</v>
       </c>
@@ -56575,47 +60608,53 @@
       <c r="A80" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="B80" s="4" t="n">
+      <c r="B80" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D80" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A80)</f>
         <v>226.97</v>
       </c>
-      <c r="C80" s="5" t="n">
-        <f aca="false">B80/规则参数!$B$8</f>
+      <c r="E80" s="5" t="n">
+        <f aca="false">D80/规则参数!$B$8</f>
         <v>6.94620620822604E-006</v>
       </c>
-      <c r="D80" s="4" t="n">
+      <c r="F80" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A80)</f>
         <v>66.41</v>
       </c>
-      <c r="E80" s="5" t="n">
-        <f aca="false">D80/规则参数!$B$9</f>
+      <c r="G80" s="5" t="n">
+        <f aca="false">F80/规则参数!$B$9</f>
         <v>1.47606917679435E-005</v>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="H80" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A80)</f>
         <v>0</v>
       </c>
-      <c r="G80" s="5" t="n">
-        <f aca="false">F80/规则参数!$B$10</f>
-        <v>0</v>
-      </c>
-      <c r="H80" s="6" t="n">
-        <f aca="false">IFERROR(F80/B80,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I80" s="6" t="n">
-        <f aca="false">IFERROR(D80/B80,0)</f>
+      <c r="I80" s="5" t="n">
+        <f aca="false">H80/规则参数!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="J80" s="6" t="n">
+        <f aca="false">IFERROR(H80/D80,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K80" s="6" t="n">
+        <f aca="false">IFERROR(F80/D80,0)</f>
         <v>0.292593734854827</v>
       </c>
-      <c r="J80" s="3" t="n">
+      <c r="L80" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A80)</f>
         <v>2</v>
       </c>
-      <c r="K80" s="4" t="n">
+      <c r="M80" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A80)</f>
         <v>0</v>
       </c>
-      <c r="L80" s="4" t="n">
+      <c r="N80" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A80)</f>
         <v>0</v>
       </c>
@@ -56624,47 +60663,53 @@
       <c r="A81" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="B81" s="4" t="n">
+      <c r="B81" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D81" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A81)</f>
         <v>2527.53</v>
       </c>
-      <c r="C81" s="5" t="n">
-        <f aca="false">B81/规则参数!$B$8</f>
+      <c r="E81" s="5" t="n">
+        <f aca="false">D81/规则参数!$B$8</f>
         <v>7.73527099505555E-005</v>
       </c>
-      <c r="D81" s="4" t="n">
+      <c r="F81" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A81)</f>
         <v>-1271.1</v>
       </c>
-      <c r="E81" s="5" t="n">
-        <f aca="false">D81/规则参数!$B$9</f>
+      <c r="G81" s="5" t="n">
+        <f aca="false">F81/规则参数!$B$9</f>
         <v>-0.000282522440991312</v>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="H81" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A81)</f>
         <v>0</v>
       </c>
-      <c r="G81" s="5" t="n">
-        <f aca="false">F81/规则参数!$B$10</f>
-        <v>0</v>
-      </c>
-      <c r="H81" s="6" t="n">
-        <f aca="false">IFERROR(F81/B81,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I81" s="6" t="n">
-        <f aca="false">IFERROR(D81/B81,0)</f>
+      <c r="I81" s="5" t="n">
+        <f aca="false">H81/规则参数!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="J81" s="6" t="n">
+        <f aca="false">IFERROR(H81/D81,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K81" s="6" t="n">
+        <f aca="false">IFERROR(F81/D81,0)</f>
         <v>-0.502902042705725</v>
       </c>
-      <c r="J81" s="3" t="n">
+      <c r="L81" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A81)</f>
         <v>1</v>
       </c>
-      <c r="K81" s="4" t="n">
+      <c r="M81" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A81)</f>
         <v>0</v>
       </c>
-      <c r="L81" s="4" t="n">
+      <c r="N81" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A81)</f>
         <v>0</v>
       </c>
@@ -56673,47 +60718,53 @@
       <c r="A82" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="B82" s="4" t="n">
+      <c r="B82" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D82" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A82)</f>
         <v>92.25</v>
       </c>
-      <c r="C82" s="5" t="n">
-        <f aca="false">B82/规则参数!$B$8</f>
+      <c r="E82" s="5" t="n">
+        <f aca="false">D82/规则参数!$B$8</f>
         <v>2.82322563646673E-006</v>
       </c>
-      <c r="D82" s="4" t="n">
+      <c r="F82" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A82)</f>
         <v>-26.02</v>
       </c>
-      <c r="E82" s="5" t="n">
-        <f aca="false">D82/规则参数!$B$9</f>
+      <c r="G82" s="5" t="n">
+        <f aca="false">F82/规则参数!$B$9</f>
         <v>-5.78336394822904E-006</v>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="H82" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A82)</f>
         <v>0</v>
       </c>
-      <c r="G82" s="5" t="n">
-        <f aca="false">F82/规则参数!$B$10</f>
-        <v>0</v>
-      </c>
-      <c r="H82" s="6" t="n">
-        <f aca="false">IFERROR(F82/B82,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I82" s="6" t="n">
-        <f aca="false">IFERROR(D82/B82,0)</f>
+      <c r="I82" s="5" t="n">
+        <f aca="false">H82/规则参数!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="J82" s="6" t="n">
+        <f aca="false">IFERROR(H82/D82,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K82" s="6" t="n">
+        <f aca="false">IFERROR(F82/D82,0)</f>
         <v>-0.282059620596206</v>
       </c>
-      <c r="J82" s="3" t="n">
+      <c r="L82" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A82)</f>
         <v>1</v>
       </c>
-      <c r="K82" s="4" t="n">
+      <c r="M82" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A82)</f>
         <v>0</v>
       </c>
-      <c r="L82" s="4" t="n">
+      <c r="N82" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A82)</f>
         <v>0</v>
       </c>
@@ -56722,47 +60773,53 @@
       <c r="A83" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="B83" s="4" t="n">
+      <c r="B83" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D83" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A83)</f>
         <v>86.32</v>
       </c>
-      <c r="C83" s="5" t="n">
-        <f aca="false">B83/规则参数!$B$8</f>
+      <c r="E83" s="5" t="n">
+        <f aca="false">D83/规则参数!$B$8</f>
         <v>2.64174348986241E-006</v>
       </c>
-      <c r="D83" s="4" t="n">
+      <c r="F83" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A83)</f>
         <v>31.88</v>
       </c>
-      <c r="E83" s="5" t="n">
-        <f aca="false">D83/规则参数!$B$9</f>
+      <c r="G83" s="5" t="n">
+        <f aca="false">F83/规则参数!$B$9</f>
         <v>7.08584330013612E-006</v>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="H83" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A83)</f>
         <v>0</v>
       </c>
-      <c r="G83" s="5" t="n">
-        <f aca="false">F83/规则参数!$B$10</f>
-        <v>0</v>
-      </c>
-      <c r="H83" s="6" t="n">
-        <f aca="false">IFERROR(F83/B83,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I83" s="6" t="n">
-        <f aca="false">IFERROR(D83/B83,0)</f>
+      <c r="I83" s="5" t="n">
+        <f aca="false">H83/规则参数!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="J83" s="6" t="n">
+        <f aca="false">IFERROR(H83/D83,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <f aca="false">IFERROR(F83/D83,0)</f>
         <v>0.369323447636701</v>
       </c>
-      <c r="J83" s="3" t="n">
+      <c r="L83" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A83)</f>
         <v>2</v>
       </c>
-      <c r="K83" s="4" t="n">
+      <c r="M83" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A83)</f>
         <v>0</v>
       </c>
-      <c r="L83" s="4" t="n">
+      <c r="N83" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A83)</f>
         <v>0</v>
       </c>
@@ -56771,47 +60828,53 @@
       <c r="A84" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="B84" s="4" t="n">
+      <c r="B84" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D84" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A84)</f>
         <v>758.76</v>
       </c>
-      <c r="C84" s="5" t="n">
-        <f aca="false">B84/规则参数!$B$8</f>
+      <c r="E84" s="5" t="n">
+        <f aca="false">D84/规则参数!$B$8</f>
         <v>2.32211456252086E-005</v>
       </c>
-      <c r="D84" s="4" t="n">
+      <c r="F84" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A84)</f>
         <v>239.31</v>
       </c>
-      <c r="E84" s="5" t="n">
-        <f aca="false">D84/规则参数!$B$9</f>
+      <c r="G84" s="5" t="n">
+        <f aca="false">F84/规则参数!$B$9</f>
         <v>5.31905006322326E-005</v>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="H84" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A84)</f>
         <v>0</v>
       </c>
-      <c r="G84" s="5" t="n">
-        <f aca="false">F84/规则参数!$B$10</f>
-        <v>0</v>
-      </c>
-      <c r="H84" s="6" t="n">
-        <f aca="false">IFERROR(F84/B84,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I84" s="6" t="n">
-        <f aca="false">IFERROR(D84/B84,0)</f>
+      <c r="I84" s="5" t="n">
+        <f aca="false">H84/规则参数!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="J84" s="6" t="n">
+        <f aca="false">IFERROR(H84/D84,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <f aca="false">IFERROR(F84/D84,0)</f>
         <v>0.315396172702831</v>
       </c>
-      <c r="J84" s="3" t="n">
+      <c r="L84" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A84)</f>
         <v>2</v>
       </c>
-      <c r="K84" s="4" t="n">
+      <c r="M84" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A84)</f>
         <v>0</v>
       </c>
-      <c r="L84" s="4" t="n">
+      <c r="N84" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A84)</f>
         <v>0</v>
       </c>
@@ -56820,47 +60883,53 @@
       <c r="A85" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="B85" s="4" t="n">
+      <c r="B85" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D85" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A85)</f>
         <v>59.51</v>
       </c>
-      <c r="C85" s="5" t="n">
-        <f aca="false">B85/规则参数!$B$8</f>
+      <c r="E85" s="5" t="n">
+        <f aca="false">D85/规则参数!$B$8</f>
         <v>1.82124832115051E-006</v>
       </c>
-      <c r="D85" s="4" t="n">
+      <c r="F85" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A85)</f>
         <v>-8.98</v>
       </c>
-      <c r="E85" s="5" t="n">
-        <f aca="false">D85/规则参数!$B$9</f>
+      <c r="G85" s="5" t="n">
+        <f aca="false">F85/规则参数!$B$9</f>
         <v>-1.99594958705214E-006</v>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="H85" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A85)</f>
         <v>0</v>
       </c>
-      <c r="G85" s="5" t="n">
-        <f aca="false">F85/规则参数!$B$10</f>
-        <v>0</v>
-      </c>
-      <c r="H85" s="6" t="n">
-        <f aca="false">IFERROR(F85/B85,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I85" s="6" t="n">
-        <f aca="false">IFERROR(D85/B85,0)</f>
+      <c r="I85" s="5" t="n">
+        <f aca="false">H85/规则参数!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="J85" s="6" t="n">
+        <f aca="false">IFERROR(H85/D85,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <f aca="false">IFERROR(F85/D85,0)</f>
         <v>-0.150899008569988</v>
       </c>
-      <c r="J85" s="3" t="n">
+      <c r="L85" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A85)</f>
         <v>1</v>
       </c>
-      <c r="K85" s="4" t="n">
+      <c r="M85" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A85)</f>
         <v>0</v>
       </c>
-      <c r="L85" s="4" t="n">
+      <c r="N85" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A85)</f>
         <v>0</v>
       </c>
@@ -56869,47 +60938,53 @@
       <c r="A86" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="B86" s="4" t="n">
+      <c r="B86" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D86" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A86)</f>
         <v>107.91</v>
       </c>
-      <c r="C86" s="5" t="n">
-        <f aca="false">B86/规则参数!$B$8</f>
+      <c r="E86" s="5" t="n">
+        <f aca="false">D86/规则参数!$B$8</f>
         <v>3.30248540304742E-006</v>
       </c>
-      <c r="D86" s="4" t="n">
+      <c r="F86" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A86)</f>
         <v>37.75</v>
       </c>
-      <c r="E86" s="5" t="n">
-        <f aca="false">D86/规则参数!$B$9</f>
+      <c r="G86" s="5" t="n">
+        <f aca="false">F86/规则参数!$B$9</f>
         <v>8.39054531305328E-006</v>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="H86" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A86)</f>
         <v>0</v>
       </c>
-      <c r="G86" s="5" t="n">
-        <f aca="false">F86/规则参数!$B$10</f>
-        <v>0</v>
-      </c>
-      <c r="H86" s="6" t="n">
-        <f aca="false">IFERROR(F86/B86,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I86" s="6" t="n">
-        <f aca="false">IFERROR(D86/B86,0)</f>
+      <c r="I86" s="5" t="n">
+        <f aca="false">H86/规则参数!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <f aca="false">IFERROR(H86/D86,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <f aca="false">IFERROR(F86/D86,0)</f>
         <v>0.349828560837735</v>
       </c>
-      <c r="J86" s="3" t="n">
+      <c r="L86" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A86)</f>
         <v>1</v>
       </c>
-      <c r="K86" s="4" t="n">
+      <c r="M86" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A86)</f>
         <v>0</v>
       </c>
-      <c r="L86" s="4" t="n">
+      <c r="N86" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A86)</f>
         <v>0</v>
       </c>
@@ -56918,47 +60993,53 @@
       <c r="A87" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="B87" s="4" t="n">
+      <c r="B87" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D87" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A87)</f>
         <v>45.81</v>
       </c>
-      <c r="C87" s="5" t="n">
-        <f aca="false">B87/规则参数!$B$8</f>
+      <c r="E87" s="5" t="n">
+        <f aca="false">D87/规则参数!$B$8</f>
         <v>1.40197253557226E-006</v>
       </c>
-      <c r="D87" s="4" t="n">
+      <c r="F87" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A87)</f>
         <v>15.34</v>
       </c>
-      <c r="E87" s="5" t="n">
-        <f aca="false">D87/规则参数!$B$9</f>
+      <c r="G87" s="5" t="n">
+        <f aca="false">F87/规则参数!$B$9</f>
         <v>3.40956198946324E-006</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="H87" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A87)</f>
         <v>0</v>
       </c>
-      <c r="G87" s="5" t="n">
-        <f aca="false">F87/规则参数!$B$10</f>
-        <v>0</v>
-      </c>
-      <c r="H87" s="6" t="n">
-        <f aca="false">IFERROR(F87/B87,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I87" s="6" t="n">
-        <f aca="false">IFERROR(D87/B87,0)</f>
+      <c r="I87" s="5" t="n">
+        <f aca="false">H87/规则参数!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <f aca="false">IFERROR(H87/D87,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <f aca="false">IFERROR(F87/D87,0)</f>
         <v>0.334861383977298</v>
       </c>
-      <c r="J87" s="3" t="n">
+      <c r="L87" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A87)</f>
         <v>1</v>
       </c>
-      <c r="K87" s="4" t="n">
+      <c r="M87" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A87)</f>
         <v>0</v>
       </c>
-      <c r="L87" s="4" t="n">
+      <c r="N87" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A87)</f>
         <v>0</v>
       </c>
@@ -56967,52 +61048,77 @@
       <c r="A88" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="B88" s="4" t="n">
+      <c r="B88" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D88" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$E:$E,SPU监控与预算!$A:$A,$A88)</f>
         <v>2193.1</v>
       </c>
-      <c r="C88" s="5" t="n">
-        <f aca="false">B88/规则参数!$B$8</f>
+      <c r="E88" s="5" t="n">
+        <f aca="false">D88/规则参数!$B$8</f>
         <v>6.7117790171655E-005</v>
       </c>
-      <c r="D88" s="4" t="n">
+      <c r="F88" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$G:$G,SPU监控与预算!$A:$A,$A88)</f>
         <v>886.22</v>
       </c>
-      <c r="E88" s="5" t="n">
-        <f aca="false">D88/规则参数!$B$9</f>
+      <c r="G88" s="5" t="n">
+        <f aca="false">F88/规则参数!$B$9</f>
         <v>0.00019697666403534</v>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="H88" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$I:$I,SPU监控与预算!$A:$A,$A88)</f>
         <v>-0.5</v>
       </c>
-      <c r="G88" s="5" t="n">
-        <f aca="false">F88/规则参数!$B$10</f>
+      <c r="I88" s="5" t="n">
+        <f aca="false">H88/规则参数!$B$10</f>
         <v>-1.03268705897692E-007</v>
       </c>
-      <c r="H88" s="6" t="n">
-        <f aca="false">IFERROR(F88/B88,0)</f>
+      <c r="J88" s="6" t="n">
+        <f aca="false">IFERROR(H88/D88,0)</f>
         <v>-0.000227987779855</v>
       </c>
-      <c r="I88" s="6" t="n">
-        <f aca="false">IFERROR(D88/B88,0)</f>
+      <c r="K88" s="6" t="n">
+        <f aca="false">IFERROR(F88/D88,0)</f>
         <v>0.404094660526196</v>
       </c>
-      <c r="J88" s="3" t="n">
+      <c r="L88" s="3" t="n">
         <f aca="false">COUNTIFS(SPU监控与预算!$A:$A,$A88)</f>
         <v>2</v>
       </c>
-      <c r="K88" s="4" t="n">
+      <c r="M88" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$W:$W,SPU监控与预算!$A:$A,$A88)</f>
         <v>-0.0724360865540149</v>
       </c>
-      <c r="L88" s="4" t="n">
+      <c r="N88" s="4" t="n">
         <f aca="false">SUMIFS(SPU监控与预算!$X:$X,SPU监控与预算!$A:$A,$A88)</f>
         <v>-0.085443</v>
       </c>
     </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="3" t="s">
+        <v>650</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B88">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>$B2="收缩"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>$B2="观察"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+      <formula>$B2="加投"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+      <formula>$B2="维稳"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -57038,29 +61144,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>575</v>
+        <v>651</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>576</v>
+        <v>652</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>577</v>
+        <v>653</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>578</v>
+        <v>654</v>
       </c>
       <c r="B2" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>579</v>
+        <v>655</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>580</v>
+        <v>656</v>
       </c>
       <c r="B3" s="8" t="n">
         <v>0.18</v>
@@ -57069,29 +61175,29 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>581</v>
+        <v>657</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>0.25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>582</v>
+        <v>658</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>583</v>
+        <v>659</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>0.05</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>584</v>
+        <v>660</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>585</v>
+        <v>661</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>0.15</v>
@@ -57100,29 +61206,29 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>586</v>
+        <v>662</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>587</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>588</v>
+        <v>664</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>32675390.45</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>589</v>
+        <v>665</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>590</v>
+        <v>666</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>4499111.63</v>
@@ -57131,7 +61237,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>591</v>
+        <v>667</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>4841737.83</v>
